--- a/data/RECAUDO_PF.xlsx
+++ b/data/RECAUDO_PF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://funerariaimchile.sharepoint.com/sites/CARTERAVALLESUNIDOS/Shared Documents/Cobranza/2025/MAYO 2026/07-05-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6423BB15-1D83-47ED-935B-6BFBBD651171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E5764EE-C2BF-4006-8DA4-74CA9B7C36A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7068" uniqueCount="1190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7586" uniqueCount="1277">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -3590,6 +3590,267 @@
   </si>
   <si>
     <t>954061656</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>17241987-9</t>
+  </si>
+  <si>
+    <t>SALINAS SALINAS CAMILO ANDRES</t>
+  </si>
+  <si>
+    <t>camilo.salinas89@gmail.com</t>
+  </si>
+  <si>
+    <t>949508704</t>
+  </si>
+  <si>
+    <t>07/02/2025</t>
+  </si>
+  <si>
+    <t>10693767-2</t>
+  </si>
+  <si>
+    <t>PACHECO VIVEROS LETICIA SOLEDAD</t>
+  </si>
+  <si>
+    <t>Vitacura</t>
+  </si>
+  <si>
+    <t>leticiapachecoviveros@gmail.com</t>
+  </si>
+  <si>
+    <t>965896509</t>
+  </si>
+  <si>
+    <t>994329189</t>
+  </si>
+  <si>
+    <t>06/01/2026</t>
+  </si>
+  <si>
+    <t>10706660-8</t>
+  </si>
+  <si>
+    <t>CARTER GONZALES ROBERTO GERMAN</t>
+  </si>
+  <si>
+    <t>roberto.carter@grupocerromoreno.cl</t>
+  </si>
+  <si>
+    <t>979988262</t>
+  </si>
+  <si>
+    <t>14/10/2025</t>
+  </si>
+  <si>
+    <t>5351195-3</t>
+  </si>
+  <si>
+    <t>VALDES INOSTROZA ESTANISLAO DEL CARMEN</t>
+  </si>
+  <si>
+    <t>tanyvaldesinostroza@gmail.com</t>
+  </si>
+  <si>
+    <t>993323212</t>
+  </si>
+  <si>
+    <t>12/05/2025</t>
+  </si>
+  <si>
+    <t>10506783-6</t>
+  </si>
+  <si>
+    <t>GARRIDO MERA SANDRA DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>sandragarridomera12@gmail.com</t>
+  </si>
+  <si>
+    <t>988114795</t>
+  </si>
+  <si>
+    <t>12879044-6</t>
+  </si>
+  <si>
+    <t>ACOSTA PINO VERÓNICA FLORENTICA</t>
+  </si>
+  <si>
+    <t>zoeclo46@gmail.com</t>
+  </si>
+  <si>
+    <t>959079259</t>
+  </si>
+  <si>
+    <t>ANA ROSA BURBOA FERNANDEZ</t>
+  </si>
+  <si>
+    <t>24/12/2024</t>
+  </si>
+  <si>
+    <t>12668958-6</t>
+  </si>
+  <si>
+    <t>GONZALEZ MUÑOZ JENNY ANDREA</t>
+  </si>
+  <si>
+    <t>jenny.gonzalez01936@gmail.com</t>
+  </si>
+  <si>
+    <t>984060823</t>
+  </si>
+  <si>
+    <t>8116330-8</t>
+  </si>
+  <si>
+    <t>GUERRA ZAGAL CECILIA ANGELICA</t>
+  </si>
+  <si>
+    <t>San Ramón</t>
+  </si>
+  <si>
+    <t>angelicaguerra4059@gmail.com</t>
+  </si>
+  <si>
+    <t>993615020</t>
+  </si>
+  <si>
+    <t>7896837-0</t>
+  </si>
+  <si>
+    <t>MUÑOZ SALAZAR ROSA ADELAIDA</t>
+  </si>
+  <si>
+    <t>RRojas</t>
+  </si>
+  <si>
+    <t>rosaadelaida1957@gmail.com</t>
+  </si>
+  <si>
+    <t>950980306</t>
+  </si>
+  <si>
+    <t>05/12/2025</t>
+  </si>
+  <si>
+    <t>10947894-6</t>
+  </si>
+  <si>
+    <t>IBARRA PAILLAO MARIA LILIANA</t>
+  </si>
+  <si>
+    <t>Mlilybarra@gmail.com</t>
+  </si>
+  <si>
+    <t>990877741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emperatriz Alexandra Franco Mosquera </t>
+  </si>
+  <si>
+    <t>10882279-1</t>
+  </si>
+  <si>
+    <t>BADILLA PAREDES JOSE RIGOBERTO</t>
+  </si>
+  <si>
+    <t>26325144-8</t>
+  </si>
+  <si>
+    <t>clascondes</t>
+  </si>
+  <si>
+    <t>HASTA 60 D</t>
+  </si>
+  <si>
+    <t>jobadilla1966@gmail.com</t>
+  </si>
+  <si>
+    <t>953659587</t>
+  </si>
+  <si>
+    <t>7849847-1</t>
+  </si>
+  <si>
+    <t>GALVEZ VARGAS ALICIA DEDEL CARMEN</t>
+  </si>
+  <si>
+    <t>aliciagalvezv@gmail.com</t>
+  </si>
+  <si>
+    <t>942097690</t>
+  </si>
+  <si>
+    <t>931306476</t>
+  </si>
+  <si>
+    <t>ANGELICA MARIA MUÑOZ YAÑEZ</t>
+  </si>
+  <si>
+    <t>07/11/2024</t>
+  </si>
+  <si>
+    <t>9625116-5</t>
+  </si>
+  <si>
+    <t>MORENO MIRANDA MARISOL DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MARISOLCARMENMORENO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>989244061</t>
+  </si>
+  <si>
+    <t>6389577-6</t>
+  </si>
+  <si>
+    <t>MARTINEZ MIRANDA VICTORIA DE LAS MERCEDES</t>
+  </si>
+  <si>
+    <t>VICTORIAMIRANDA73MARTINEZ@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>968401212</t>
+  </si>
+  <si>
+    <t>RICARDO JAVIER NAIPIL BURGOS</t>
+  </si>
+  <si>
+    <t>11650516-9</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ CACERES EUGENIA DE LAS MERCEDES</t>
+  </si>
+  <si>
+    <t>kenita.rodriguez70@gmail.com</t>
+  </si>
+  <si>
+    <t>990032443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">María Isabel Gutiérrez  </t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>19936540-1</t>
+  </si>
+  <si>
+    <t>ARZOLA GUTIERREZ MARÍA JOSE</t>
+  </si>
+  <si>
+    <t>kote27.arzola@hotmail.com</t>
+  </si>
+  <si>
+    <t>932405178</t>
+  </si>
+  <si>
+    <t>988044270</t>
   </si>
 </sst>
 </file>
@@ -3966,7 +4227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AV258"/>
+  <dimension ref="A1:AV277"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.796875" customWidth="1"/>
@@ -38034,10 +38295,2514 @@
         <v>1189</v>
       </c>
     </row>
+    <row r="259" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>48</v>
+      </c>
+      <c r="B259" t="s">
+        <v>138</v>
+      </c>
+      <c r="C259" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D259" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E259" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F259" t="s">
+        <v>53</v>
+      </c>
+      <c r="G259" t="s">
+        <v>111</v>
+      </c>
+      <c r="H259" t="s">
+        <v>55</v>
+      </c>
+      <c r="I259">
+        <v>3832</v>
+      </c>
+      <c r="J259" t="s">
+        <v>56</v>
+      </c>
+      <c r="K259">
+        <v>53438</v>
+      </c>
+      <c r="L259">
+        <v>53438</v>
+      </c>
+      <c r="M259">
+        <v>48</v>
+      </c>
+      <c r="N259">
+        <v>7</v>
+      </c>
+      <c r="O259" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P259">
+        <v>53438</v>
+      </c>
+      <c r="Q259">
+        <v>53438</v>
+      </c>
+      <c r="R259" t="s">
+        <v>58</v>
+      </c>
+      <c r="S259">
+        <v>46</v>
+      </c>
+      <c r="T259">
+        <v>1</v>
+      </c>
+      <c r="U259">
+        <v>1</v>
+      </c>
+      <c r="V259">
+        <v>1</v>
+      </c>
+      <c r="W259" t="s">
+        <v>59</v>
+      </c>
+      <c r="X259" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y259" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z259" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA259" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB259" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD259" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE259" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF259" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG259">
+        <v>-31</v>
+      </c>
+      <c r="AH259">
+        <v>0</v>
+      </c>
+      <c r="AI259">
+        <v>0</v>
+      </c>
+      <c r="AJ259" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK259" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL259" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM259">
+        <v>971855</v>
+      </c>
+      <c r="AN259">
+        <v>135171</v>
+      </c>
+      <c r="AS259" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT259" t="s">
+        <v>1193</v>
+      </c>
+      <c r="AV259" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="260" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>48</v>
+      </c>
+      <c r="B260" t="s">
+        <v>323</v>
+      </c>
+      <c r="C260" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D260" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E260" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F260" t="s">
+        <v>53</v>
+      </c>
+      <c r="G260" t="s">
+        <v>1198</v>
+      </c>
+      <c r="H260" t="s">
+        <v>104</v>
+      </c>
+      <c r="I260">
+        <v>565</v>
+      </c>
+      <c r="J260" t="s">
+        <v>56</v>
+      </c>
+      <c r="K260">
+        <v>40000</v>
+      </c>
+      <c r="L260">
+        <v>40000</v>
+      </c>
+      <c r="M260">
+        <v>36</v>
+      </c>
+      <c r="N260">
+        <v>7</v>
+      </c>
+      <c r="O260" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P260">
+        <v>40000</v>
+      </c>
+      <c r="Q260">
+        <v>40000</v>
+      </c>
+      <c r="R260" t="s">
+        <v>58</v>
+      </c>
+      <c r="S260">
+        <v>21</v>
+      </c>
+      <c r="T260">
+        <v>15</v>
+      </c>
+      <c r="U260">
+        <v>1</v>
+      </c>
+      <c r="V260">
+        <v>15</v>
+      </c>
+      <c r="W260" t="s">
+        <v>59</v>
+      </c>
+      <c r="X260" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y260" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z260" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA260" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB260" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC260" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD260" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE260" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF260" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG260">
+        <v>-31</v>
+      </c>
+      <c r="AH260">
+        <v>0</v>
+      </c>
+      <c r="AI260">
+        <v>0</v>
+      </c>
+      <c r="AJ260" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK260" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL260" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM260">
+        <v>971856</v>
+      </c>
+      <c r="AN260">
+        <v>133446</v>
+      </c>
+      <c r="AS260" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT260" t="s">
+        <v>1199</v>
+      </c>
+      <c r="AU260" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AV260" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="261" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>48</v>
+      </c>
+      <c r="B261" t="s">
+        <v>504</v>
+      </c>
+      <c r="C261" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D261" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E261" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F261" t="s">
+        <v>53</v>
+      </c>
+      <c r="G261" t="s">
+        <v>111</v>
+      </c>
+      <c r="H261" t="s">
+        <v>55</v>
+      </c>
+      <c r="I261">
+        <v>3055</v>
+      </c>
+      <c r="J261" t="s">
+        <v>56</v>
+      </c>
+      <c r="K261">
+        <v>86364</v>
+      </c>
+      <c r="L261">
+        <v>86364</v>
+      </c>
+      <c r="M261">
+        <v>66</v>
+      </c>
+      <c r="N261">
+        <v>7</v>
+      </c>
+      <c r="O261" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P261">
+        <v>86364</v>
+      </c>
+      <c r="Q261">
+        <v>86364</v>
+      </c>
+      <c r="R261" t="s">
+        <v>58</v>
+      </c>
+      <c r="S261">
+        <v>62</v>
+      </c>
+      <c r="T261">
+        <v>4</v>
+      </c>
+      <c r="U261">
+        <v>1</v>
+      </c>
+      <c r="V261">
+        <v>4</v>
+      </c>
+      <c r="W261" t="s">
+        <v>59</v>
+      </c>
+      <c r="X261" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y261" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z261" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA261" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB261" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD261" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE261" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF261" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG261">
+        <v>-31</v>
+      </c>
+      <c r="AH261">
+        <v>0</v>
+      </c>
+      <c r="AI261">
+        <v>0</v>
+      </c>
+      <c r="AJ261" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK261" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL261" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM261">
+        <v>971857</v>
+      </c>
+      <c r="AN261">
+        <v>134957</v>
+      </c>
+      <c r="AS261" t="s">
+        <v>312</v>
+      </c>
+      <c r="AT261" t="s">
+        <v>1205</v>
+      </c>
+      <c r="AU261" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV261" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="262" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>48</v>
+      </c>
+      <c r="B262" t="s">
+        <v>331</v>
+      </c>
+      <c r="C262" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D262" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E262" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F262" t="s">
+        <v>53</v>
+      </c>
+      <c r="G262" t="s">
+        <v>54</v>
+      </c>
+      <c r="H262" t="s">
+        <v>55</v>
+      </c>
+      <c r="I262">
+        <v>1908</v>
+      </c>
+      <c r="J262" t="s">
+        <v>56</v>
+      </c>
+      <c r="K262">
+        <v>75833</v>
+      </c>
+      <c r="L262">
+        <v>75833</v>
+      </c>
+      <c r="M262">
+        <v>36</v>
+      </c>
+      <c r="N262">
+        <v>23</v>
+      </c>
+      <c r="O262" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P262">
+        <v>75833</v>
+      </c>
+      <c r="Q262">
+        <v>75833</v>
+      </c>
+      <c r="R262" t="s">
+        <v>58</v>
+      </c>
+      <c r="S262">
+        <v>26</v>
+      </c>
+      <c r="T262">
+        <v>10</v>
+      </c>
+      <c r="U262">
+        <v>1</v>
+      </c>
+      <c r="V262">
+        <v>9</v>
+      </c>
+      <c r="W262" t="s">
+        <v>59</v>
+      </c>
+      <c r="X262" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y262" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z262" t="s">
+        <v>425</v>
+      </c>
+      <c r="AA262" t="s">
+        <v>425</v>
+      </c>
+      <c r="AB262" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD262" t="s">
+        <v>426</v>
+      </c>
+      <c r="AE262" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF262" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG262">
+        <v>-139</v>
+      </c>
+      <c r="AH262">
+        <v>0</v>
+      </c>
+      <c r="AI262">
+        <v>0</v>
+      </c>
+      <c r="AJ262" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK262" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL262" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM262">
+        <v>971859</v>
+      </c>
+      <c r="AN262">
+        <v>134599</v>
+      </c>
+      <c r="AS262" t="s">
+        <v>268</v>
+      </c>
+      <c r="AT262" t="s">
+        <v>1210</v>
+      </c>
+      <c r="AU262" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV262" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="263" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>48</v>
+      </c>
+      <c r="B263" t="s">
+        <v>331</v>
+      </c>
+      <c r="C263" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D263" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E263" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F263" t="s">
+        <v>53</v>
+      </c>
+      <c r="G263" t="s">
+        <v>54</v>
+      </c>
+      <c r="H263" t="s">
+        <v>55</v>
+      </c>
+      <c r="I263">
+        <v>1908</v>
+      </c>
+      <c r="J263" t="s">
+        <v>56</v>
+      </c>
+      <c r="K263">
+        <v>75833</v>
+      </c>
+      <c r="L263">
+        <v>75833</v>
+      </c>
+      <c r="M263">
+        <v>36</v>
+      </c>
+      <c r="N263">
+        <v>23</v>
+      </c>
+      <c r="O263" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P263">
+        <v>75833</v>
+      </c>
+      <c r="Q263">
+        <v>75833</v>
+      </c>
+      <c r="R263" t="s">
+        <v>58</v>
+      </c>
+      <c r="S263">
+        <v>26</v>
+      </c>
+      <c r="T263">
+        <v>10</v>
+      </c>
+      <c r="U263">
+        <v>1</v>
+      </c>
+      <c r="V263">
+        <v>10</v>
+      </c>
+      <c r="W263" t="s">
+        <v>59</v>
+      </c>
+      <c r="X263" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y263" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z263" t="s">
+        <v>425</v>
+      </c>
+      <c r="AA263" t="s">
+        <v>425</v>
+      </c>
+      <c r="AB263" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD263" t="s">
+        <v>426</v>
+      </c>
+      <c r="AE263" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF263" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG263">
+        <v>-139</v>
+      </c>
+      <c r="AH263">
+        <v>0</v>
+      </c>
+      <c r="AI263">
+        <v>0</v>
+      </c>
+      <c r="AJ263" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK263" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL263" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM263">
+        <v>971859</v>
+      </c>
+      <c r="AN263">
+        <v>134599</v>
+      </c>
+      <c r="AS263" t="s">
+        <v>268</v>
+      </c>
+      <c r="AT263" t="s">
+        <v>1210</v>
+      </c>
+      <c r="AU263" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV263" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="264" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>48</v>
+      </c>
+      <c r="B264" t="s">
+        <v>70</v>
+      </c>
+      <c r="C264" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D264" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E264" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F264" t="s">
+        <v>53</v>
+      </c>
+      <c r="G264" t="s">
+        <v>84</v>
+      </c>
+      <c r="H264" t="s">
+        <v>55</v>
+      </c>
+      <c r="I264">
+        <v>1213</v>
+      </c>
+      <c r="J264" t="s">
+        <v>56</v>
+      </c>
+      <c r="K264">
+        <v>104167</v>
+      </c>
+      <c r="L264">
+        <v>104167</v>
+      </c>
+      <c r="M264">
+        <v>24</v>
+      </c>
+      <c r="N264">
+        <v>8</v>
+      </c>
+      <c r="O264" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P264">
+        <v>104146</v>
+      </c>
+      <c r="Q264">
+        <v>104146</v>
+      </c>
+      <c r="R264" t="s">
+        <v>58</v>
+      </c>
+      <c r="S264">
+        <v>11</v>
+      </c>
+      <c r="T264">
+        <v>14</v>
+      </c>
+      <c r="U264">
+        <v>1</v>
+      </c>
+      <c r="V264">
+        <v>13</v>
+      </c>
+      <c r="W264" t="s">
+        <v>59</v>
+      </c>
+      <c r="X264" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y264" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z264" t="s">
+        <v>550</v>
+      </c>
+      <c r="AA264" t="s">
+        <v>550</v>
+      </c>
+      <c r="AB264" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC264" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD264" t="s">
+        <v>543</v>
+      </c>
+      <c r="AE264" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF264" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG264">
+        <v>-32</v>
+      </c>
+      <c r="AH264">
+        <v>0</v>
+      </c>
+      <c r="AI264">
+        <v>0</v>
+      </c>
+      <c r="AJ264" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK264" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL264" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM264">
+        <v>971861</v>
+      </c>
+      <c r="AN264">
+        <v>134242</v>
+      </c>
+      <c r="AS264" t="s">
+        <v>120</v>
+      </c>
+      <c r="AT264" t="s">
+        <v>1215</v>
+      </c>
+      <c r="AU264" t="s">
+        <v>1216</v>
+      </c>
+      <c r="AV264" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="265" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>48</v>
+      </c>
+      <c r="B265" t="s">
+        <v>70</v>
+      </c>
+      <c r="C265" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D265" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E265" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F265" t="s">
+        <v>53</v>
+      </c>
+      <c r="G265" t="s">
+        <v>84</v>
+      </c>
+      <c r="H265" t="s">
+        <v>55</v>
+      </c>
+      <c r="I265">
+        <v>1213</v>
+      </c>
+      <c r="J265" t="s">
+        <v>56</v>
+      </c>
+      <c r="K265">
+        <v>104167</v>
+      </c>
+      <c r="L265">
+        <v>104167</v>
+      </c>
+      <c r="M265">
+        <v>24</v>
+      </c>
+      <c r="N265">
+        <v>8</v>
+      </c>
+      <c r="O265" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P265">
+        <v>21</v>
+      </c>
+      <c r="Q265">
+        <v>21</v>
+      </c>
+      <c r="R265" t="s">
+        <v>58</v>
+      </c>
+      <c r="S265">
+        <v>11</v>
+      </c>
+      <c r="T265">
+        <v>14</v>
+      </c>
+      <c r="U265">
+        <v>1</v>
+      </c>
+      <c r="V265">
+        <v>14</v>
+      </c>
+      <c r="W265" t="s">
+        <v>59</v>
+      </c>
+      <c r="X265" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y265" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z265" t="s">
+        <v>550</v>
+      </c>
+      <c r="AA265" t="s">
+        <v>550</v>
+      </c>
+      <c r="AB265" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC265" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD265" t="s">
+        <v>543</v>
+      </c>
+      <c r="AE265" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF265" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG265">
+        <v>-32</v>
+      </c>
+      <c r="AH265">
+        <v>0</v>
+      </c>
+      <c r="AI265">
+        <v>0</v>
+      </c>
+      <c r="AJ265" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK265" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL265" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM265">
+        <v>971861</v>
+      </c>
+      <c r="AN265">
+        <v>134242</v>
+      </c>
+      <c r="AS265" t="s">
+        <v>120</v>
+      </c>
+      <c r="AT265" t="s">
+        <v>1215</v>
+      </c>
+      <c r="AU265" t="s">
+        <v>1216</v>
+      </c>
+      <c r="AV265" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="266" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>48</v>
+      </c>
+      <c r="B266" t="s">
+        <v>316</v>
+      </c>
+      <c r="C266" t="s">
+        <v>377</v>
+      </c>
+      <c r="D266" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E266" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F266" t="s">
+        <v>53</v>
+      </c>
+      <c r="G266" t="s">
+        <v>408</v>
+      </c>
+      <c r="H266" t="s">
+        <v>55</v>
+      </c>
+      <c r="I266">
+        <v>2918</v>
+      </c>
+      <c r="J266" t="s">
+        <v>56</v>
+      </c>
+      <c r="K266">
+        <v>25500</v>
+      </c>
+      <c r="L266">
+        <v>25500</v>
+      </c>
+      <c r="M266">
+        <v>60</v>
+      </c>
+      <c r="N266">
+        <v>5</v>
+      </c>
+      <c r="O266" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P266">
+        <v>500</v>
+      </c>
+      <c r="Q266">
+        <v>500</v>
+      </c>
+      <c r="R266" t="s">
+        <v>58</v>
+      </c>
+      <c r="S266">
+        <v>56</v>
+      </c>
+      <c r="T266">
+        <v>4</v>
+      </c>
+      <c r="U266">
+        <v>1</v>
+      </c>
+      <c r="V266">
+        <v>4</v>
+      </c>
+      <c r="W266" t="s">
+        <v>59</v>
+      </c>
+      <c r="X266" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y266" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z266" t="s">
+        <v>550</v>
+      </c>
+      <c r="AA266" t="s">
+        <v>550</v>
+      </c>
+      <c r="AB266" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD266" t="s">
+        <v>543</v>
+      </c>
+      <c r="AE266" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF266" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG266">
+        <v>-29</v>
+      </c>
+      <c r="AH266">
+        <v>7</v>
+      </c>
+      <c r="AI266">
+        <v>0</v>
+      </c>
+      <c r="AJ266" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK266" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL266" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM266">
+        <v>971863</v>
+      </c>
+      <c r="AN266">
+        <v>134905</v>
+      </c>
+      <c r="AS266" t="s">
+        <v>202</v>
+      </c>
+      <c r="AT266" t="s">
+        <v>1219</v>
+      </c>
+      <c r="AU266" t="s">
+        <v>1220</v>
+      </c>
+      <c r="AV266" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="267" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>48</v>
+      </c>
+      <c r="B267" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C267" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D267" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E267" t="s">
+        <v>1224</v>
+      </c>
+      <c r="F267" t="s">
+        <v>53</v>
+      </c>
+      <c r="G267" t="s">
+        <v>209</v>
+      </c>
+      <c r="H267" t="s">
+        <v>104</v>
+      </c>
+      <c r="I267">
+        <v>373</v>
+      </c>
+      <c r="J267" t="s">
+        <v>56</v>
+      </c>
+      <c r="K267">
+        <v>47500</v>
+      </c>
+      <c r="L267">
+        <v>47500</v>
+      </c>
+      <c r="M267">
+        <v>24</v>
+      </c>
+      <c r="N267">
+        <v>6</v>
+      </c>
+      <c r="O267" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P267">
+        <v>47500</v>
+      </c>
+      <c r="Q267">
+        <v>47500</v>
+      </c>
+      <c r="R267" t="s">
+        <v>58</v>
+      </c>
+      <c r="S267">
+        <v>8</v>
+      </c>
+      <c r="T267">
+        <v>16</v>
+      </c>
+      <c r="U267">
+        <v>1</v>
+      </c>
+      <c r="V267">
+        <v>16</v>
+      </c>
+      <c r="W267" t="s">
+        <v>59</v>
+      </c>
+      <c r="X267" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y267" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z267" t="s">
+        <v>550</v>
+      </c>
+      <c r="AA267" t="s">
+        <v>550</v>
+      </c>
+      <c r="AB267" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC267" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD267" t="s">
+        <v>543</v>
+      </c>
+      <c r="AE267" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF267" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG267">
+        <v>-30</v>
+      </c>
+      <c r="AH267">
+        <v>0</v>
+      </c>
+      <c r="AI267">
+        <v>0</v>
+      </c>
+      <c r="AJ267" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK267" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL267" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM267">
+        <v>971865</v>
+      </c>
+      <c r="AN267">
+        <v>133371</v>
+      </c>
+      <c r="AS267" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT267" t="s">
+        <v>1225</v>
+      </c>
+      <c r="AU267" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV267" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="268" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>48</v>
+      </c>
+      <c r="B268" t="s">
+        <v>353</v>
+      </c>
+      <c r="C268" t="s">
+        <v>837</v>
+      </c>
+      <c r="D268" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E268" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F268" t="s">
+        <v>53</v>
+      </c>
+      <c r="G268" t="s">
+        <v>1229</v>
+      </c>
+      <c r="H268" t="s">
+        <v>55</v>
+      </c>
+      <c r="I268">
+        <v>2797</v>
+      </c>
+      <c r="J268" t="s">
+        <v>56</v>
+      </c>
+      <c r="K268">
+        <v>40000</v>
+      </c>
+      <c r="L268">
+        <v>40000</v>
+      </c>
+      <c r="M268">
+        <v>35</v>
+      </c>
+      <c r="N268">
+        <v>30</v>
+      </c>
+      <c r="O268" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P268">
+        <v>40000</v>
+      </c>
+      <c r="Q268">
+        <v>40000</v>
+      </c>
+      <c r="R268" t="s">
+        <v>58</v>
+      </c>
+      <c r="S268">
+        <v>30</v>
+      </c>
+      <c r="T268">
+        <v>5</v>
+      </c>
+      <c r="U268">
+        <v>1</v>
+      </c>
+      <c r="V268">
+        <v>5</v>
+      </c>
+      <c r="W268" t="s">
+        <v>59</v>
+      </c>
+      <c r="X268" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y268" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z268" t="s">
+        <v>550</v>
+      </c>
+      <c r="AA268" t="s">
+        <v>550</v>
+      </c>
+      <c r="AB268" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD268" t="s">
+        <v>543</v>
+      </c>
+      <c r="AE268" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF268" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG268">
+        <v>-54</v>
+      </c>
+      <c r="AH268">
+        <v>0</v>
+      </c>
+      <c r="AI268">
+        <v>0</v>
+      </c>
+      <c r="AJ268" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK268" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL268" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM268">
+        <v>971867</v>
+      </c>
+      <c r="AN268">
+        <v>134874</v>
+      </c>
+      <c r="AS268" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT268" t="s">
+        <v>1230</v>
+      </c>
+      <c r="AU268" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV268" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="269" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>48</v>
+      </c>
+      <c r="B269" t="s">
+        <v>559</v>
+      </c>
+      <c r="C269" t="s">
+        <v>737</v>
+      </c>
+      <c r="D269" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E269" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F269" t="s">
+        <v>53</v>
+      </c>
+      <c r="G269" t="s">
+        <v>119</v>
+      </c>
+      <c r="H269" t="s">
+        <v>55</v>
+      </c>
+      <c r="I269">
+        <v>2841</v>
+      </c>
+      <c r="J269" t="s">
+        <v>56</v>
+      </c>
+      <c r="K269">
+        <v>35000</v>
+      </c>
+      <c r="L269">
+        <v>35000</v>
+      </c>
+      <c r="M269">
+        <v>36</v>
+      </c>
+      <c r="N269">
+        <v>5</v>
+      </c>
+      <c r="O269" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P269">
+        <v>35000</v>
+      </c>
+      <c r="Q269">
+        <v>35000</v>
+      </c>
+      <c r="R269" t="s">
+        <v>58</v>
+      </c>
+      <c r="S269">
+        <v>34</v>
+      </c>
+      <c r="T269">
+        <v>2</v>
+      </c>
+      <c r="U269">
+        <v>1</v>
+      </c>
+      <c r="V269">
+        <v>2</v>
+      </c>
+      <c r="W269" t="s">
+        <v>59</v>
+      </c>
+      <c r="X269" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y269" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z269" t="s">
+        <v>1234</v>
+      </c>
+      <c r="AA269" t="s">
+        <v>1234</v>
+      </c>
+      <c r="AB269" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD269" t="s">
+        <v>187</v>
+      </c>
+      <c r="AE269" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF269" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG269">
+        <v>-29</v>
+      </c>
+      <c r="AH269">
+        <v>0</v>
+      </c>
+      <c r="AI269">
+        <v>0</v>
+      </c>
+      <c r="AJ269" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK269" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL269" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM269">
+        <v>971869</v>
+      </c>
+      <c r="AN269">
+        <v>134884</v>
+      </c>
+      <c r="AS269" t="s">
+        <v>202</v>
+      </c>
+      <c r="AT269" t="s">
+        <v>1235</v>
+      </c>
+      <c r="AV269" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="270" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>48</v>
+      </c>
+      <c r="B270" t="s">
+        <v>49</v>
+      </c>
+      <c r="C270" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D270" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E270" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F270" t="s">
+        <v>53</v>
+      </c>
+      <c r="G270" t="s">
+        <v>54</v>
+      </c>
+      <c r="H270" t="s">
+        <v>55</v>
+      </c>
+      <c r="I270">
+        <v>2660</v>
+      </c>
+      <c r="J270" t="s">
+        <v>56</v>
+      </c>
+      <c r="K270">
+        <v>30000</v>
+      </c>
+      <c r="L270">
+        <v>30000</v>
+      </c>
+      <c r="M270">
+        <v>60</v>
+      </c>
+      <c r="N270">
+        <v>5</v>
+      </c>
+      <c r="O270" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P270">
+        <v>30000</v>
+      </c>
+      <c r="Q270">
+        <v>30000</v>
+      </c>
+      <c r="R270" t="s">
+        <v>58</v>
+      </c>
+      <c r="S270">
+        <v>55</v>
+      </c>
+      <c r="T270">
+        <v>5</v>
+      </c>
+      <c r="U270">
+        <v>1</v>
+      </c>
+      <c r="V270">
+        <v>5</v>
+      </c>
+      <c r="W270" t="s">
+        <v>59</v>
+      </c>
+      <c r="X270" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y270" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z270" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA270" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB270" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD270" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE270" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF270" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG270">
+        <v>-29</v>
+      </c>
+      <c r="AH270">
+        <v>0</v>
+      </c>
+      <c r="AI270">
+        <v>0</v>
+      </c>
+      <c r="AJ270" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK270" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL270" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM270">
+        <v>971870</v>
+      </c>
+      <c r="AN270">
+        <v>134834</v>
+      </c>
+      <c r="AS270" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT270" t="s">
+        <v>1240</v>
+      </c>
+      <c r="AU270" t="s">
+        <v>1241</v>
+      </c>
+      <c r="AV270" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="271" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>48</v>
+      </c>
+      <c r="B271" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C271" t="s">
+        <v>782</v>
+      </c>
+      <c r="D271" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E271" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F271" t="s">
+        <v>53</v>
+      </c>
+      <c r="G271" t="s">
+        <v>311</v>
+      </c>
+      <c r="H271" t="s">
+        <v>55</v>
+      </c>
+      <c r="I271">
+        <v>2332</v>
+      </c>
+      <c r="J271" t="s">
+        <v>56</v>
+      </c>
+      <c r="K271">
+        <v>25000</v>
+      </c>
+      <c r="L271">
+        <v>25000</v>
+      </c>
+      <c r="M271">
+        <v>60</v>
+      </c>
+      <c r="N271">
+        <v>5</v>
+      </c>
+      <c r="O271" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P271">
+        <v>25000</v>
+      </c>
+      <c r="Q271">
+        <v>25000</v>
+      </c>
+      <c r="R271" t="s">
+        <v>58</v>
+      </c>
+      <c r="S271">
+        <v>55</v>
+      </c>
+      <c r="T271">
+        <v>5</v>
+      </c>
+      <c r="U271">
+        <v>1</v>
+      </c>
+      <c r="V271">
+        <v>5</v>
+      </c>
+      <c r="W271" t="s">
+        <v>59</v>
+      </c>
+      <c r="X271" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y271" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z271" t="s">
+        <v>1245</v>
+      </c>
+      <c r="AA271" t="s">
+        <v>1245</v>
+      </c>
+      <c r="AB271" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD271" t="s">
+        <v>1246</v>
+      </c>
+      <c r="AE271" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF271" t="s">
+        <v>1247</v>
+      </c>
+      <c r="AG271">
+        <v>2</v>
+      </c>
+      <c r="AH271">
+        <v>0</v>
+      </c>
+      <c r="AI271">
+        <v>0</v>
+      </c>
+      <c r="AJ271" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK271" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL271" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM271">
+        <v>971880</v>
+      </c>
+      <c r="AN271">
+        <v>134735</v>
+      </c>
+      <c r="AS271" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT271" t="s">
+        <v>1248</v>
+      </c>
+      <c r="AU271" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV271" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="272" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>48</v>
+      </c>
+      <c r="B272" t="s">
+        <v>676</v>
+      </c>
+      <c r="C272" t="s">
+        <v>279</v>
+      </c>
+      <c r="D272" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E272" t="s">
+        <v>1251</v>
+      </c>
+      <c r="F272" t="s">
+        <v>53</v>
+      </c>
+      <c r="G272" t="s">
+        <v>119</v>
+      </c>
+      <c r="H272" t="s">
+        <v>75</v>
+      </c>
+      <c r="I272">
+        <v>1571</v>
+      </c>
+      <c r="J272" t="s">
+        <v>56</v>
+      </c>
+      <c r="K272">
+        <v>33750</v>
+      </c>
+      <c r="L272">
+        <v>33750</v>
+      </c>
+      <c r="M272">
+        <v>48</v>
+      </c>
+      <c r="N272">
+        <v>10</v>
+      </c>
+      <c r="O272" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P272">
+        <v>33500</v>
+      </c>
+      <c r="Q272">
+        <v>33500</v>
+      </c>
+      <c r="R272" t="s">
+        <v>58</v>
+      </c>
+      <c r="S272">
+        <v>39</v>
+      </c>
+      <c r="T272">
+        <v>9</v>
+      </c>
+      <c r="U272">
+        <v>1</v>
+      </c>
+      <c r="V272">
+        <v>9</v>
+      </c>
+      <c r="W272" t="s">
+        <v>59</v>
+      </c>
+      <c r="X272" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y272" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z272" t="s">
+        <v>199</v>
+      </c>
+      <c r="AA272" t="s">
+        <v>199</v>
+      </c>
+      <c r="AB272" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC272" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD272" t="s">
+        <v>200</v>
+      </c>
+      <c r="AE272" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF272" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG272">
+        <v>-95</v>
+      </c>
+      <c r="AH272">
+        <v>30</v>
+      </c>
+      <c r="AI272">
+        <v>0</v>
+      </c>
+      <c r="AJ272" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK272" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL272" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM272">
+        <v>971882</v>
+      </c>
+      <c r="AN272">
+        <v>134428</v>
+      </c>
+      <c r="AS272" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT272" t="s">
+        <v>1252</v>
+      </c>
+      <c r="AU272" t="s">
+        <v>1253</v>
+      </c>
+      <c r="AV272" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="273" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>48</v>
+      </c>
+      <c r="B273" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C273" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D273" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E273" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F273" t="s">
+        <v>53</v>
+      </c>
+      <c r="G273" t="s">
+        <v>882</v>
+      </c>
+      <c r="H273" t="s">
+        <v>104</v>
+      </c>
+      <c r="I273">
+        <v>149</v>
+      </c>
+      <c r="J273" t="s">
+        <v>56</v>
+      </c>
+      <c r="K273">
+        <v>28000</v>
+      </c>
+      <c r="L273">
+        <v>28000</v>
+      </c>
+      <c r="M273">
+        <v>36</v>
+      </c>
+      <c r="N273">
+        <v>5</v>
+      </c>
+      <c r="O273" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P273">
+        <v>28000</v>
+      </c>
+      <c r="Q273">
+        <v>28000</v>
+      </c>
+      <c r="R273" t="s">
+        <v>58</v>
+      </c>
+      <c r="S273">
+        <v>18</v>
+      </c>
+      <c r="T273">
+        <v>18</v>
+      </c>
+      <c r="U273">
+        <v>1</v>
+      </c>
+      <c r="V273">
+        <v>18</v>
+      </c>
+      <c r="W273" t="s">
+        <v>7</v>
+      </c>
+      <c r="X273" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y273" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z273" t="s">
+        <v>550</v>
+      </c>
+      <c r="AA273" t="s">
+        <v>550</v>
+      </c>
+      <c r="AB273" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC273" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD273" t="s">
+        <v>543</v>
+      </c>
+      <c r="AE273" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF273" t="s">
+        <v>409</v>
+      </c>
+      <c r="AG273">
+        <v>-29</v>
+      </c>
+      <c r="AH273">
+        <v>0</v>
+      </c>
+      <c r="AI273">
+        <v>0</v>
+      </c>
+      <c r="AJ273" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK273" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL273" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM273">
+        <v>971884</v>
+      </c>
+      <c r="AN273">
+        <v>133305</v>
+      </c>
+      <c r="AS273" t="s">
+        <v>202</v>
+      </c>
+      <c r="AT273" t="s">
+        <v>1259</v>
+      </c>
+      <c r="AU273" t="s">
+        <v>1260</v>
+      </c>
+      <c r="AV273" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="274" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>48</v>
+      </c>
+      <c r="B274" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C274" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D274" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E274" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F274" t="s">
+        <v>53</v>
+      </c>
+      <c r="G274" t="s">
+        <v>882</v>
+      </c>
+      <c r="H274" t="s">
+        <v>104</v>
+      </c>
+      <c r="I274">
+        <v>147</v>
+      </c>
+      <c r="J274" t="s">
+        <v>56</v>
+      </c>
+      <c r="K274">
+        <v>36000</v>
+      </c>
+      <c r="L274">
+        <v>36000</v>
+      </c>
+      <c r="M274">
+        <v>36</v>
+      </c>
+      <c r="N274">
+        <v>5</v>
+      </c>
+      <c r="O274" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P274">
+        <v>36000</v>
+      </c>
+      <c r="Q274">
+        <v>36000</v>
+      </c>
+      <c r="R274" t="s">
+        <v>58</v>
+      </c>
+      <c r="S274">
+        <v>18</v>
+      </c>
+      <c r="T274">
+        <v>18</v>
+      </c>
+      <c r="U274">
+        <v>1</v>
+      </c>
+      <c r="V274">
+        <v>18</v>
+      </c>
+      <c r="W274" t="s">
+        <v>7</v>
+      </c>
+      <c r="X274" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y274" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z274" t="s">
+        <v>550</v>
+      </c>
+      <c r="AA274" t="s">
+        <v>550</v>
+      </c>
+      <c r="AB274" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC274" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD274" t="s">
+        <v>543</v>
+      </c>
+      <c r="AE274" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF274" t="s">
+        <v>409</v>
+      </c>
+      <c r="AG274">
+        <v>-29</v>
+      </c>
+      <c r="AH274">
+        <v>0</v>
+      </c>
+      <c r="AI274">
+        <v>0</v>
+      </c>
+      <c r="AJ274" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK274" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL274" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM274">
+        <v>971886</v>
+      </c>
+      <c r="AN274">
+        <v>133288</v>
+      </c>
+      <c r="AS274" t="s">
+        <v>225</v>
+      </c>
+      <c r="AT274" t="s">
+        <v>1263</v>
+      </c>
+      <c r="AU274" t="s">
+        <v>1264</v>
+      </c>
+      <c r="AV274" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="275" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>48</v>
+      </c>
+      <c r="B275" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C275" t="s">
+        <v>723</v>
+      </c>
+      <c r="D275" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E275" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F275" t="s">
+        <v>53</v>
+      </c>
+      <c r="G275" t="s">
+        <v>452</v>
+      </c>
+      <c r="H275" t="s">
+        <v>55</v>
+      </c>
+      <c r="I275">
+        <v>2415</v>
+      </c>
+      <c r="J275" t="s">
+        <v>56</v>
+      </c>
+      <c r="K275">
+        <v>42500</v>
+      </c>
+      <c r="L275">
+        <v>42500</v>
+      </c>
+      <c r="M275">
+        <v>36</v>
+      </c>
+      <c r="N275">
+        <v>1</v>
+      </c>
+      <c r="O275" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P275">
+        <v>42500</v>
+      </c>
+      <c r="Q275">
+        <v>42500</v>
+      </c>
+      <c r="R275" t="s">
+        <v>58</v>
+      </c>
+      <c r="S275">
+        <v>29</v>
+      </c>
+      <c r="T275">
+        <v>7</v>
+      </c>
+      <c r="U275">
+        <v>1</v>
+      </c>
+      <c r="V275">
+        <v>7</v>
+      </c>
+      <c r="W275" t="s">
+        <v>59</v>
+      </c>
+      <c r="X275" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y275" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z275" t="s">
+        <v>550</v>
+      </c>
+      <c r="AA275" t="s">
+        <v>550</v>
+      </c>
+      <c r="AB275" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD275" t="s">
+        <v>543</v>
+      </c>
+      <c r="AE275" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF275" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG275">
+        <v>-86</v>
+      </c>
+      <c r="AH275">
+        <v>0</v>
+      </c>
+      <c r="AI275">
+        <v>0</v>
+      </c>
+      <c r="AJ275" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK275" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL275" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM275">
+        <v>971888</v>
+      </c>
+      <c r="AN275">
+        <v>134756</v>
+      </c>
+      <c r="AS275" t="s">
+        <v>202</v>
+      </c>
+      <c r="AT275" t="s">
+        <v>1268</v>
+      </c>
+      <c r="AU275" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV275" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="276" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>48</v>
+      </c>
+      <c r="B276" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C276" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D276" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E276" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F276" t="s">
+        <v>53</v>
+      </c>
+      <c r="G276" t="s">
+        <v>452</v>
+      </c>
+      <c r="H276" t="s">
+        <v>55</v>
+      </c>
+      <c r="I276">
+        <v>3998</v>
+      </c>
+      <c r="J276" t="s">
+        <v>56</v>
+      </c>
+      <c r="K276">
+        <v>35750</v>
+      </c>
+      <c r="L276">
+        <v>35750</v>
+      </c>
+      <c r="M276">
+        <v>36</v>
+      </c>
+      <c r="N276">
+        <v>9</v>
+      </c>
+      <c r="O276" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P276">
+        <v>35750</v>
+      </c>
+      <c r="Q276">
+        <v>35750</v>
+      </c>
+      <c r="R276" t="s">
+        <v>58</v>
+      </c>
+      <c r="S276">
+        <v>35</v>
+      </c>
+      <c r="T276">
+        <v>2</v>
+      </c>
+      <c r="U276">
+        <v>1</v>
+      </c>
+      <c r="V276">
+        <v>1</v>
+      </c>
+      <c r="W276" t="s">
+        <v>59</v>
+      </c>
+      <c r="X276" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y276" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z276" t="s">
+        <v>550</v>
+      </c>
+      <c r="AA276" t="s">
+        <v>550</v>
+      </c>
+      <c r="AB276" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD276" t="s">
+        <v>543</v>
+      </c>
+      <c r="AE276" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF276" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG276">
+        <v>-33</v>
+      </c>
+      <c r="AH276">
+        <v>0</v>
+      </c>
+      <c r="AI276">
+        <v>0</v>
+      </c>
+      <c r="AJ276" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK276" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL276" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM276">
+        <v>971890</v>
+      </c>
+      <c r="AN276">
+        <v>135208</v>
+      </c>
+      <c r="AS276" t="s">
+        <v>202</v>
+      </c>
+      <c r="AT276" t="s">
+        <v>1274</v>
+      </c>
+      <c r="AU276" t="s">
+        <v>1275</v>
+      </c>
+      <c r="AV276" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="277" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>48</v>
+      </c>
+      <c r="B277" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C277" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D277" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E277" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F277" t="s">
+        <v>53</v>
+      </c>
+      <c r="G277" t="s">
+        <v>452</v>
+      </c>
+      <c r="H277" t="s">
+        <v>55</v>
+      </c>
+      <c r="I277">
+        <v>3998</v>
+      </c>
+      <c r="J277" t="s">
+        <v>56</v>
+      </c>
+      <c r="K277">
+        <v>35750</v>
+      </c>
+      <c r="L277">
+        <v>35750</v>
+      </c>
+      <c r="M277">
+        <v>36</v>
+      </c>
+      <c r="N277">
+        <v>9</v>
+      </c>
+      <c r="O277" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P277">
+        <v>2000</v>
+      </c>
+      <c r="Q277">
+        <v>2000</v>
+      </c>
+      <c r="R277" t="s">
+        <v>58</v>
+      </c>
+      <c r="S277">
+        <v>35</v>
+      </c>
+      <c r="T277">
+        <v>2</v>
+      </c>
+      <c r="U277">
+        <v>1</v>
+      </c>
+      <c r="V277">
+        <v>2</v>
+      </c>
+      <c r="W277" t="s">
+        <v>59</v>
+      </c>
+      <c r="X277" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y277" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z277" t="s">
+        <v>550</v>
+      </c>
+      <c r="AA277" t="s">
+        <v>550</v>
+      </c>
+      <c r="AB277" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD277" t="s">
+        <v>543</v>
+      </c>
+      <c r="AE277" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF277" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG277">
+        <v>-33</v>
+      </c>
+      <c r="AH277">
+        <v>0</v>
+      </c>
+      <c r="AI277">
+        <v>0</v>
+      </c>
+      <c r="AJ277" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK277" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL277" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM277">
+        <v>971890</v>
+      </c>
+      <c r="AN277">
+        <v>135208</v>
+      </c>
+      <c r="AS277" t="s">
+        <v>202</v>
+      </c>
+      <c r="AT277" t="s">
+        <v>1274</v>
+      </c>
+      <c r="AU277" t="s">
+        <v>1275</v>
+      </c>
+      <c r="AV277" t="s">
+        <v>1276</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AV258" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AV277" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -38258,13 +41023,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7E3B6AB-27EB-4F9F-8365-4BF40A6CCD02}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C59DCED-5F63-43D6-B8D8-81E621B5A6A1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDDB2C88-4B0E-427D-AA90-F20137981B9F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E8098D5-7410-4870-BAC7-6609AEB8FB6C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{791BBE6B-688E-4179-B895-34F2EAA5A859}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2424B923-134C-4B06-AB06-0A75CC9D5A01}"/>
 </file>
--- a/data/RECAUDO_PF.xlsx
+++ b/data/RECAUDO_PF.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://funerariaimchile.sharepoint.com/sites/CARTERAVALLESUNIDOS/Shared Documents/Cobranza/2025/JUNIO 2026/04-06-2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://funerariaimchile.sharepoint.com/sites/CARTERAVALLESUNIDOS/Shared Documents/Cobranza/2025/JUNIO 2026/05-06-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE387B74-C601-4435-BE76-F41D3DF1EC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{068E8E75-7D27-4D77-BAD8-A3E948482AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6803" uniqueCount="904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8570" uniqueCount="1124">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -2732,6 +2732,666 @@
   </si>
   <si>
     <t>UGARTE CANALES ALFONSO ALBERTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTER YOLANDA DEL CARMEN SAAVEDRA ESCOBAR </t>
+  </si>
+  <si>
+    <t>18832851-2</t>
+  </si>
+  <si>
+    <t>SAAVEDRA ESCOBAR ESTER YOLANDA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>05/06/2026</t>
+  </si>
+  <si>
+    <t>SAAVEDRAESTER63@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>971614786</t>
+  </si>
+  <si>
+    <t>01/07/2025</t>
+  </si>
+  <si>
+    <t>6961758-1</t>
+  </si>
+  <si>
+    <t>GALLARDO TRIGO ALEJANDRINA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>FHernandez</t>
+  </si>
+  <si>
+    <t>carola4336.mateo@gmail.com</t>
+  </si>
+  <si>
+    <t>989618797</t>
+  </si>
+  <si>
+    <t>9280479-8</t>
+  </si>
+  <si>
+    <t>TORO PARA ELSA AMADA</t>
+  </si>
+  <si>
+    <t>cmjorquerat@gmail.com</t>
+  </si>
+  <si>
+    <t>991979574</t>
+  </si>
+  <si>
+    <t>AIRON CRISTOFER ORELLANA MORAGA</t>
+  </si>
+  <si>
+    <t>29/11/2024</t>
+  </si>
+  <si>
+    <t>17421873-0</t>
+  </si>
+  <si>
+    <t>CANTILLANA FERNANDEZ MIGUEL SANTIAGO</t>
+  </si>
+  <si>
+    <t>santiagocantillana@gmail.com</t>
+  </si>
+  <si>
+    <t>977814616</t>
+  </si>
+  <si>
+    <t>7554831-1</t>
+  </si>
+  <si>
+    <t>FERNADEZ JARAMILLO EDILIA</t>
+  </si>
+  <si>
+    <t>17/12/2024</t>
+  </si>
+  <si>
+    <t>13085236-K</t>
+  </si>
+  <si>
+    <t>SOTO MASQUERAN PAULA ANDREA</t>
+  </si>
+  <si>
+    <t>psoto@alfacom.cl</t>
+  </si>
+  <si>
+    <t>995456662</t>
+  </si>
+  <si>
+    <t>19/03/2025</t>
+  </si>
+  <si>
+    <t>10380047-1</t>
+  </si>
+  <si>
+    <t>GONZALEZ MONTECINO JOSE LUIS</t>
+  </si>
+  <si>
+    <t>jose-gonzalez72@hotmail.com</t>
+  </si>
+  <si>
+    <t>942860487</t>
+  </si>
+  <si>
+    <t>949297874</t>
+  </si>
+  <si>
+    <t>30/06/2025</t>
+  </si>
+  <si>
+    <t>15533942-K</t>
+  </si>
+  <si>
+    <t>MEZA PEREZ LUIS ERNESTO</t>
+  </si>
+  <si>
+    <t>luis.meza1583@gmail.com</t>
+  </si>
+  <si>
+    <t>939450927</t>
+  </si>
+  <si>
+    <t>13674610-3</t>
+  </si>
+  <si>
+    <t>MEZA ROMERO ADRIAN ESTEBAN</t>
+  </si>
+  <si>
+    <t>adriabmezaromero1979@gmail.com</t>
+  </si>
+  <si>
+    <t>959041594</t>
+  </si>
+  <si>
+    <t>STEFANI SOLEDAD PAVEZ SILVA</t>
+  </si>
+  <si>
+    <t>29/07/2025</t>
+  </si>
+  <si>
+    <t>10437403-4</t>
+  </si>
+  <si>
+    <t>GODOY HIDALGO LORENA ANTONIETA</t>
+  </si>
+  <si>
+    <t>loregodoy@gmail.com</t>
+  </si>
+  <si>
+    <t>975582880</t>
+  </si>
+  <si>
+    <t>31/10/2025</t>
+  </si>
+  <si>
+    <t>18497588-2</t>
+  </si>
+  <si>
+    <t>DONOSO DONOSO ADOLFO MOISES</t>
+  </si>
+  <si>
+    <t>El Bosque</t>
+  </si>
+  <si>
+    <t>adolfo.donoso.d@gmail.com</t>
+  </si>
+  <si>
+    <t>999751542</t>
+  </si>
+  <si>
+    <t>11144542-7</t>
+  </si>
+  <si>
+    <t>OLGUIN HERRERA SILVIA ISABEL</t>
+  </si>
+  <si>
+    <t>insumoscaballero@gmail.com</t>
+  </si>
+  <si>
+    <t>997334300</t>
+  </si>
+  <si>
+    <t>07/11/2025</t>
+  </si>
+  <si>
+    <t>9906220-7</t>
+  </si>
+  <si>
+    <t>ARAVENA CID JULIO GILBERTO</t>
+  </si>
+  <si>
+    <t>julioac1964@gmail.com</t>
+  </si>
+  <si>
+    <t>976378863</t>
+  </si>
+  <si>
+    <t>KIMBERLY ASHLEY AHUMADA LEITON</t>
+  </si>
+  <si>
+    <t>7363310-9</t>
+  </si>
+  <si>
+    <t>DONOSO ISMAEL JUAN</t>
+  </si>
+  <si>
+    <t>juandonosoulloa55@gmail.com</t>
+  </si>
+  <si>
+    <t>941650570</t>
+  </si>
+  <si>
+    <t>08/12/2025</t>
+  </si>
+  <si>
+    <t>14630574-1</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ LEMUNAO ROBERTO ESTEBAN</t>
+  </si>
+  <si>
+    <t>ROBERTORODRIGUEZLEMUNAO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>986438179</t>
+  </si>
+  <si>
+    <t>13061930-4</t>
+  </si>
+  <si>
+    <t>ASTRELLI MARTINEZ SANDY PAULINA</t>
+  </si>
+  <si>
+    <t>SANDY_3090_9030@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>977610152</t>
+  </si>
+  <si>
+    <t>16085591-6</t>
+  </si>
+  <si>
+    <t>CORREA VALENZUELA MARÍA JOSE</t>
+  </si>
+  <si>
+    <t>correa.valenzuela@gmail.com</t>
+  </si>
+  <si>
+    <t>977505182</t>
+  </si>
+  <si>
+    <t>RODRIGO ANDRES ALVAREZ INOSTROZA</t>
+  </si>
+  <si>
+    <t>8245177-3</t>
+  </si>
+  <si>
+    <t>FREDERICK SANTIBAÑEZ PABLO MIGUEL</t>
+  </si>
+  <si>
+    <t>pablofrederick26@gmail.com</t>
+  </si>
+  <si>
+    <t>968443055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veronica cecilia gonzalez morales </t>
+  </si>
+  <si>
+    <t>18/02/2026</t>
+  </si>
+  <si>
+    <t>6920834-7</t>
+  </si>
+  <si>
+    <t>SAAVEDRA PLAZA ROSA</t>
+  </si>
+  <si>
+    <t>jafralni.14@gmail.com</t>
+  </si>
+  <si>
+    <t>988344728</t>
+  </si>
+  <si>
+    <t>Joaquin Neves Silva</t>
+  </si>
+  <si>
+    <t>14418684-2</t>
+  </si>
+  <si>
+    <t>SLIEPIZZA  DOLORES</t>
+  </si>
+  <si>
+    <t>C.E.</t>
+  </si>
+  <si>
+    <t>mgpannes@gmail.com</t>
+  </si>
+  <si>
+    <t>954570150</t>
+  </si>
+  <si>
+    <t>28/03/2026</t>
+  </si>
+  <si>
+    <t>9211459-7</t>
+  </si>
+  <si>
+    <t>FERNANDEZ ROZAS MARINA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>AJaspe</t>
+  </si>
+  <si>
+    <t>AMORDEHIJO667@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>985959805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jocelyn Karen Acevedo Acevedo </t>
+  </si>
+  <si>
+    <t>17/12/2025</t>
+  </si>
+  <si>
+    <t>9431322-8</t>
+  </si>
+  <si>
+    <t>CONTRERAS SAN MARTIN MARIA ELIZABETH</t>
+  </si>
+  <si>
+    <t>elizabethcontrerassanmartin@gmail.com</t>
+  </si>
+  <si>
+    <t>996829002</t>
+  </si>
+  <si>
+    <t>ALINE ALEJANDRA MUÑOZ PEREZ</t>
+  </si>
+  <si>
+    <t>9037581-4</t>
+  </si>
+  <si>
+    <t>TAPIA DIAZ XIMENA ALBINA</t>
+  </si>
+  <si>
+    <t>XTAPIA@AUTOMARCO.COM</t>
+  </si>
+  <si>
+    <t>999678770</t>
+  </si>
+  <si>
+    <t>14173400-8</t>
+  </si>
+  <si>
+    <t>CASTRO MORAGA JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>josecastro316@hotmail.com</t>
+  </si>
+  <si>
+    <t>921611689</t>
+  </si>
+  <si>
+    <t>RICARDO JAVIER NAIPIL BURGOS</t>
+  </si>
+  <si>
+    <t>11650516-9</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ CACERES EUGENIA DE LAS MERCEDES</t>
+  </si>
+  <si>
+    <t>kenita.rodriguez70@gmail.com</t>
+  </si>
+  <si>
+    <t>990032443</t>
+  </si>
+  <si>
+    <t>5529497-6</t>
+  </si>
+  <si>
+    <t>RIVEROS RODRIGUEZ LEONEL HUMBERTO</t>
+  </si>
+  <si>
+    <t>990475887</t>
+  </si>
+  <si>
+    <t>995385970</t>
+  </si>
+  <si>
+    <t>8719769-7</t>
+  </si>
+  <si>
+    <t>LEIVA AVILA ROSA ALICIA</t>
+  </si>
+  <si>
+    <t>RoxanaR</t>
+  </si>
+  <si>
+    <t>cpajaritos</t>
+  </si>
+  <si>
+    <t>rosileivaavi@gmail.com</t>
+  </si>
+  <si>
+    <t>984182099</t>
+  </si>
+  <si>
+    <t>6872848-7</t>
+  </si>
+  <si>
+    <t>BUSTOS SANCHEZ MARIO ALBERTO</t>
+  </si>
+  <si>
+    <t>mariobustoss@gmail.com</t>
+  </si>
+  <si>
+    <t>966188055</t>
+  </si>
+  <si>
+    <t>13/05/2026</t>
+  </si>
+  <si>
+    <t>9783316-8</t>
+  </si>
+  <si>
+    <t>LIZAMA LOBOS JEANNETTE INGRID</t>
+  </si>
+  <si>
+    <t>JEANETTE1962LIZAMA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>935496324</t>
+  </si>
+  <si>
+    <t>26/08/2025</t>
+  </si>
+  <si>
+    <t>6294931-7</t>
+  </si>
+  <si>
+    <t>ALFARO SANCHEZ ANA MARIA</t>
+  </si>
+  <si>
+    <t>Biobío</t>
+  </si>
+  <si>
+    <t>San Carlos</t>
+  </si>
+  <si>
+    <t>anitamaria.alfaro@gmail.com</t>
+  </si>
+  <si>
+    <t>991010715</t>
+  </si>
+  <si>
+    <t>ANGELICA MARIA MUÑOZ YAÑEZ</t>
+  </si>
+  <si>
+    <t>07/11/2024</t>
+  </si>
+  <si>
+    <t>9625116-5</t>
+  </si>
+  <si>
+    <t>MORENO MIRANDA MARISOL DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MARISOLCARMENMORENO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>989244061</t>
+  </si>
+  <si>
+    <t>15/04/2025</t>
+  </si>
+  <si>
+    <t>5629763-4</t>
+  </si>
+  <si>
+    <t>GARCIA SERRANO NATALIA GEORGINA</t>
+  </si>
+  <si>
+    <t>nela_2005gonza@hotmail.com</t>
+  </si>
+  <si>
+    <t>998975123</t>
+  </si>
+  <si>
+    <t>6389577-6</t>
+  </si>
+  <si>
+    <t>MARTINEZ MIRANDA VICTORIA DE LAS MERCEDES</t>
+  </si>
+  <si>
+    <t>VICTORIAMIRANDA73MARTINEZ@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>968401212</t>
+  </si>
+  <si>
+    <t>06/08/2025</t>
+  </si>
+  <si>
+    <t>10085131-8</t>
+  </si>
+  <si>
+    <t>GARCIA DIAZ MARIA VERONICA</t>
+  </si>
+  <si>
+    <t>verito.garcia.diaz1963@gmail.com</t>
+  </si>
+  <si>
+    <t>996241952</t>
+  </si>
+  <si>
+    <t>CONSTANZA BELEN LOBOS PEDREROS</t>
+  </si>
+  <si>
+    <t>16/02/2026</t>
+  </si>
+  <si>
+    <t>14188915-K</t>
+  </si>
+  <si>
+    <t>PEDREROS LOPEZ SILVIA ADELA</t>
+  </si>
+  <si>
+    <t>silviapedreros@hotmail.com</t>
+  </si>
+  <si>
+    <t>971428075</t>
+  </si>
+  <si>
+    <t>5668283-K</t>
+  </si>
+  <si>
+    <t>BAHAMONDEZ BURGOS LUCIA DE JESUS</t>
+  </si>
+  <si>
+    <t>angeseguel1964@gmail.com</t>
+  </si>
+  <si>
+    <t>977711691</t>
+  </si>
+  <si>
+    <t>29/12/2025</t>
+  </si>
+  <si>
+    <t>20121903-5</t>
+  </si>
+  <si>
+    <t>ALDAY CORONA PAULA</t>
+  </si>
+  <si>
+    <t>San José de Maipo</t>
+  </si>
+  <si>
+    <t>paulaaldaycorona@gmail.com</t>
+  </si>
+  <si>
+    <t>944708745</t>
+  </si>
+  <si>
+    <t>7150629-0</t>
+  </si>
+  <si>
+    <t>FUENZALIDA PIZARRO ENZO ENRIQUE</t>
+  </si>
+  <si>
+    <t>jakiefuenzalida@gmail.com</t>
+  </si>
+  <si>
+    <t>984076290</t>
+  </si>
+  <si>
+    <t>PAULA VIRGINIA ORTEGA RAMIREZ</t>
+  </si>
+  <si>
+    <t>28/02/2026</t>
+  </si>
+  <si>
+    <t>8562252-8</t>
+  </si>
+  <si>
+    <t>SARMIENTO PAREDES JUANA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>20482093-7</t>
+  </si>
+  <si>
+    <t>cviña</t>
+  </si>
+  <si>
+    <t>sarmientoparedes.juana@gmail.com</t>
+  </si>
+  <si>
+    <t>944041708</t>
+  </si>
+  <si>
+    <t>LISSETE  OLIVARES ARANCIBIA</t>
+  </si>
+  <si>
+    <t>09/11/2024</t>
+  </si>
+  <si>
+    <t>9070609-8</t>
+  </si>
+  <si>
+    <t>RUBIO SCHIAFFINO SUSANA ISMENIA</t>
+  </si>
+  <si>
+    <t>rubioschiaffino80@gmail.com</t>
+  </si>
+  <si>
+    <t>935444978</t>
+  </si>
+  <si>
+    <t>10170200-6</t>
+  </si>
+  <si>
+    <t>MUÑOZ ZAMORA ANA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>22081986jeannette@gmail.com</t>
+  </si>
+  <si>
+    <t>979628954</t>
+  </si>
+  <si>
+    <t>11/03/2025</t>
+  </si>
+  <si>
+    <t>11970622-K</t>
+  </si>
+  <si>
+    <t>SILVA AMPUERO ANGÉLICA YANETH</t>
+  </si>
+  <si>
+    <t>yanet.silva.ampuero@gmail.com</t>
+  </si>
+  <si>
+    <t>958548786</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
+  </si>
+  <si>
+    <t>12873178-4</t>
+  </si>
+  <si>
+    <t>URZUA GODOY PAOLA ANDREA</t>
+  </si>
+  <si>
+    <t>andy.urzua@gmail.com</t>
+  </si>
+  <si>
+    <t>961910887</t>
   </si>
 </sst>
 </file>
@@ -3108,16 +3768,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AV249"/>
+  <dimension ref="A1:AV314"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.796875" customWidth="1"/>
-    <col min="2" max="2" width="41.796875" customWidth="1"/>
+    <col min="2" max="2" width="44.796875" customWidth="1"/>
     <col min="3" max="3" width="16.796875" customWidth="1"/>
     <col min="4" max="4" width="14.796875" customWidth="1"/>
     <col min="5" max="5" width="48.796875" customWidth="1"/>
     <col min="6" max="6" width="15.796875" customWidth="1"/>
-    <col min="7" max="7" width="18.796875" customWidth="1"/>
+    <col min="7" max="7" width="19.796875" customWidth="1"/>
     <col min="8" max="8" width="27.796875" customWidth="1"/>
     <col min="9" max="10" width="17.796875" customWidth="1"/>
     <col min="11" max="11" width="13.796875" customWidth="1"/>
@@ -14854,10 +15514,10 @@
         <v>58</v>
       </c>
       <c r="S89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T89">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U89">
         <v>1</v>
@@ -14893,10 +15553,10 @@
         <v>63</v>
       </c>
       <c r="AG89">
-        <v>-127</v>
+        <v>-158</v>
       </c>
       <c r="AH89">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI89">
         <v>0</v>
@@ -35841,17 +36501,8565 @@
         <v>901</v>
       </c>
     </row>
+    <row r="250" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>48</v>
+      </c>
+      <c r="B250" t="s">
+        <v>904</v>
+      </c>
+      <c r="C250" t="s">
+        <v>574</v>
+      </c>
+      <c r="D250" t="s">
+        <v>905</v>
+      </c>
+      <c r="E250" t="s">
+        <v>906</v>
+      </c>
+      <c r="F250" t="s">
+        <v>53</v>
+      </c>
+      <c r="G250" t="s">
+        <v>553</v>
+      </c>
+      <c r="H250" t="s">
+        <v>108</v>
+      </c>
+      <c r="I250">
+        <v>1559</v>
+      </c>
+      <c r="J250" t="s">
+        <v>56</v>
+      </c>
+      <c r="K250">
+        <v>36000</v>
+      </c>
+      <c r="L250">
+        <v>36000</v>
+      </c>
+      <c r="M250">
+        <v>60</v>
+      </c>
+      <c r="N250">
+        <v>5</v>
+      </c>
+      <c r="O250" t="s">
+        <v>907</v>
+      </c>
+      <c r="P250">
+        <v>36000</v>
+      </c>
+      <c r="Q250">
+        <v>36000</v>
+      </c>
+      <c r="R250" t="s">
+        <v>58</v>
+      </c>
+      <c r="S250">
+        <v>52</v>
+      </c>
+      <c r="T250">
+        <v>8</v>
+      </c>
+      <c r="U250">
+        <v>1</v>
+      </c>
+      <c r="V250">
+        <v>8</v>
+      </c>
+      <c r="W250" t="s">
+        <v>90</v>
+      </c>
+      <c r="X250" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y250" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z250" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA250" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB250" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC250" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD250" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE250" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF250" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG250">
+        <v>-30</v>
+      </c>
+      <c r="AH250">
+        <v>0</v>
+      </c>
+      <c r="AI250">
+        <v>0</v>
+      </c>
+      <c r="AJ250" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK250" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL250" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM250">
+        <v>973569</v>
+      </c>
+      <c r="AN250">
+        <v>134432</v>
+      </c>
+      <c r="AS250" t="s">
+        <v>99</v>
+      </c>
+      <c r="AT250" t="s">
+        <v>908</v>
+      </c>
+      <c r="AV250" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="251" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>48</v>
+      </c>
+      <c r="B251" t="s">
+        <v>163</v>
+      </c>
+      <c r="C251" t="s">
+        <v>910</v>
+      </c>
+      <c r="D251" t="s">
+        <v>911</v>
+      </c>
+      <c r="E251" t="s">
+        <v>912</v>
+      </c>
+      <c r="F251" t="s">
+        <v>53</v>
+      </c>
+      <c r="G251" t="s">
+        <v>147</v>
+      </c>
+      <c r="H251" t="s">
+        <v>108</v>
+      </c>
+      <c r="I251">
+        <v>1411</v>
+      </c>
+      <c r="J251" t="s">
+        <v>56</v>
+      </c>
+      <c r="K251">
+        <v>35000</v>
+      </c>
+      <c r="L251">
+        <v>35000</v>
+      </c>
+      <c r="M251">
+        <v>60</v>
+      </c>
+      <c r="N251">
+        <v>10</v>
+      </c>
+      <c r="O251" t="s">
+        <v>907</v>
+      </c>
+      <c r="P251">
+        <v>35000</v>
+      </c>
+      <c r="Q251">
+        <v>35000</v>
+      </c>
+      <c r="R251" t="s">
+        <v>58</v>
+      </c>
+      <c r="S251">
+        <v>48</v>
+      </c>
+      <c r="T251">
+        <v>12</v>
+      </c>
+      <c r="U251">
+        <v>1</v>
+      </c>
+      <c r="V251">
+        <v>12</v>
+      </c>
+      <c r="W251" t="s">
+        <v>7</v>
+      </c>
+      <c r="X251" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y251" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z251" t="s">
+        <v>913</v>
+      </c>
+      <c r="AA251" t="s">
+        <v>913</v>
+      </c>
+      <c r="AB251" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC251" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD251" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE251" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF251" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG251">
+        <v>-35</v>
+      </c>
+      <c r="AH251">
+        <v>0</v>
+      </c>
+      <c r="AI251">
+        <v>0</v>
+      </c>
+      <c r="AJ251" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK251" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL251" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM251">
+        <v>973571</v>
+      </c>
+      <c r="AN251">
+        <v>134343</v>
+      </c>
+      <c r="AS251" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT251" t="s">
+        <v>914</v>
+      </c>
+      <c r="AV251" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="252" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>48</v>
+      </c>
+      <c r="B252" t="s">
+        <v>609</v>
+      </c>
+      <c r="C252" t="s">
+        <v>761</v>
+      </c>
+      <c r="D252" t="s">
+        <v>916</v>
+      </c>
+      <c r="E252" t="s">
+        <v>917</v>
+      </c>
+      <c r="F252" t="s">
+        <v>53</v>
+      </c>
+      <c r="G252" t="s">
+        <v>147</v>
+      </c>
+      <c r="H252" t="s">
+        <v>108</v>
+      </c>
+      <c r="I252">
+        <v>3101</v>
+      </c>
+      <c r="J252" t="s">
+        <v>56</v>
+      </c>
+      <c r="K252">
+        <v>42708</v>
+      </c>
+      <c r="L252">
+        <v>42708</v>
+      </c>
+      <c r="M252">
+        <v>36</v>
+      </c>
+      <c r="N252">
+        <v>5</v>
+      </c>
+      <c r="O252" t="s">
+        <v>907</v>
+      </c>
+      <c r="P252">
+        <v>42708</v>
+      </c>
+      <c r="Q252">
+        <v>42708</v>
+      </c>
+      <c r="R252" t="s">
+        <v>58</v>
+      </c>
+      <c r="S252">
+        <v>31</v>
+      </c>
+      <c r="T252">
+        <v>5</v>
+      </c>
+      <c r="U252">
+        <v>1</v>
+      </c>
+      <c r="V252">
+        <v>5</v>
+      </c>
+      <c r="W252" t="s">
+        <v>90</v>
+      </c>
+      <c r="X252" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y252" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z252" t="s">
+        <v>913</v>
+      </c>
+      <c r="AA252" t="s">
+        <v>913</v>
+      </c>
+      <c r="AB252" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD252" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE252" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF252" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG252">
+        <v>-30</v>
+      </c>
+      <c r="AH252">
+        <v>0</v>
+      </c>
+      <c r="AI252">
+        <v>0</v>
+      </c>
+      <c r="AJ252" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK252" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL252" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM252">
+        <v>973573</v>
+      </c>
+      <c r="AN252">
+        <v>134971</v>
+      </c>
+      <c r="AS252" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT252" t="s">
+        <v>918</v>
+      </c>
+      <c r="AU252" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV252" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="253" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>48</v>
+      </c>
+      <c r="B253" t="s">
+        <v>920</v>
+      </c>
+      <c r="C253" t="s">
+        <v>921</v>
+      </c>
+      <c r="D253" t="s">
+        <v>922</v>
+      </c>
+      <c r="E253" t="s">
+        <v>923</v>
+      </c>
+      <c r="F253" t="s">
+        <v>53</v>
+      </c>
+      <c r="G253" t="s">
+        <v>612</v>
+      </c>
+      <c r="H253" t="s">
+        <v>89</v>
+      </c>
+      <c r="I253">
+        <v>254</v>
+      </c>
+      <c r="J253" t="s">
+        <v>56</v>
+      </c>
+      <c r="K253">
+        <v>16800</v>
+      </c>
+      <c r="L253">
+        <v>16800</v>
+      </c>
+      <c r="M253">
+        <v>60</v>
+      </c>
+      <c r="N253">
+        <v>5</v>
+      </c>
+      <c r="O253" t="s">
+        <v>907</v>
+      </c>
+      <c r="P253">
+        <v>16800</v>
+      </c>
+      <c r="Q253">
+        <v>16800</v>
+      </c>
+      <c r="R253" t="s">
+        <v>58</v>
+      </c>
+      <c r="S253">
+        <v>42</v>
+      </c>
+      <c r="T253">
+        <v>18</v>
+      </c>
+      <c r="U253">
+        <v>1</v>
+      </c>
+      <c r="V253">
+        <v>18</v>
+      </c>
+      <c r="W253" t="s">
+        <v>90</v>
+      </c>
+      <c r="X253" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y253" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z253" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA253" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB253" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC253" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD253" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE253" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF253" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG253">
+        <v>-30</v>
+      </c>
+      <c r="AH253">
+        <v>0</v>
+      </c>
+      <c r="AI253">
+        <v>0</v>
+      </c>
+      <c r="AJ253" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK253" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL253" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM253">
+        <v>973574</v>
+      </c>
+      <c r="AN253">
+        <v>133328</v>
+      </c>
+      <c r="AS253" t="s">
+        <v>177</v>
+      </c>
+      <c r="AT253" t="s">
+        <v>924</v>
+      </c>
+      <c r="AU253" t="s">
+        <v>925</v>
+      </c>
+      <c r="AV253" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="254" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>48</v>
+      </c>
+      <c r="B254" t="s">
+        <v>920</v>
+      </c>
+      <c r="C254" t="s">
+        <v>921</v>
+      </c>
+      <c r="D254" t="s">
+        <v>926</v>
+      </c>
+      <c r="E254" t="s">
+        <v>927</v>
+      </c>
+      <c r="F254" t="s">
+        <v>53</v>
+      </c>
+      <c r="G254" t="s">
+        <v>612</v>
+      </c>
+      <c r="H254" t="s">
+        <v>89</v>
+      </c>
+      <c r="I254">
+        <v>255</v>
+      </c>
+      <c r="J254" t="s">
+        <v>56</v>
+      </c>
+      <c r="K254">
+        <v>21600</v>
+      </c>
+      <c r="L254">
+        <v>21600</v>
+      </c>
+      <c r="M254">
+        <v>59</v>
+      </c>
+      <c r="N254">
+        <v>5</v>
+      </c>
+      <c r="O254" t="s">
+        <v>907</v>
+      </c>
+      <c r="P254">
+        <v>21600</v>
+      </c>
+      <c r="Q254">
+        <v>21600</v>
+      </c>
+      <c r="R254" t="s">
+        <v>58</v>
+      </c>
+      <c r="S254">
+        <v>40</v>
+      </c>
+      <c r="T254">
+        <v>19</v>
+      </c>
+      <c r="U254">
+        <v>1</v>
+      </c>
+      <c r="V254">
+        <v>19</v>
+      </c>
+      <c r="W254" t="s">
+        <v>90</v>
+      </c>
+      <c r="X254" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y254" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z254" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA254" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB254" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC254" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD254" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE254" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF254" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG254">
+        <v>-30</v>
+      </c>
+      <c r="AH254">
+        <v>0</v>
+      </c>
+      <c r="AI254">
+        <v>0</v>
+      </c>
+      <c r="AJ254" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK254" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL254" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM254">
+        <v>973575</v>
+      </c>
+      <c r="AN254">
+        <v>133329</v>
+      </c>
+      <c r="AS254" t="s">
+        <v>191</v>
+      </c>
+      <c r="AT254" t="s">
+        <v>924</v>
+      </c>
+      <c r="AU254" t="s">
+        <v>925</v>
+      </c>
+      <c r="AV254" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="255" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>48</v>
+      </c>
+      <c r="B255" t="s">
+        <v>163</v>
+      </c>
+      <c r="C255" t="s">
+        <v>928</v>
+      </c>
+      <c r="D255" t="s">
+        <v>929</v>
+      </c>
+      <c r="E255" t="s">
+        <v>930</v>
+      </c>
+      <c r="F255" t="s">
+        <v>53</v>
+      </c>
+      <c r="G255" t="s">
+        <v>147</v>
+      </c>
+      <c r="H255" t="s">
+        <v>89</v>
+      </c>
+      <c r="I255">
+        <v>340</v>
+      </c>
+      <c r="J255" t="s">
+        <v>56</v>
+      </c>
+      <c r="K255">
+        <v>48958</v>
+      </c>
+      <c r="L255">
+        <v>48958</v>
+      </c>
+      <c r="M255">
+        <v>48</v>
+      </c>
+      <c r="N255">
+        <v>5</v>
+      </c>
+      <c r="O255" t="s">
+        <v>907</v>
+      </c>
+      <c r="P255">
+        <v>48958</v>
+      </c>
+      <c r="Q255">
+        <v>48958</v>
+      </c>
+      <c r="R255" t="s">
+        <v>58</v>
+      </c>
+      <c r="S255">
+        <v>30</v>
+      </c>
+      <c r="T255">
+        <v>18</v>
+      </c>
+      <c r="U255">
+        <v>1</v>
+      </c>
+      <c r="V255">
+        <v>18</v>
+      </c>
+      <c r="W255" t="s">
+        <v>90</v>
+      </c>
+      <c r="X255" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y255" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z255" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA255" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB255" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC255" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD255" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE255" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF255" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG255">
+        <v>-30</v>
+      </c>
+      <c r="AH255">
+        <v>0</v>
+      </c>
+      <c r="AI255">
+        <v>0</v>
+      </c>
+      <c r="AJ255" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK255" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL255" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM255">
+        <v>973576</v>
+      </c>
+      <c r="AN255">
+        <v>133354</v>
+      </c>
+      <c r="AS255" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT255" t="s">
+        <v>931</v>
+      </c>
+      <c r="AV255" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="256" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>48</v>
+      </c>
+      <c r="B256" t="s">
+        <v>462</v>
+      </c>
+      <c r="C256" t="s">
+        <v>933</v>
+      </c>
+      <c r="D256" t="s">
+        <v>934</v>
+      </c>
+      <c r="E256" t="s">
+        <v>935</v>
+      </c>
+      <c r="F256" t="s">
+        <v>53</v>
+      </c>
+      <c r="G256" t="s">
+        <v>98</v>
+      </c>
+      <c r="H256" t="s">
+        <v>108</v>
+      </c>
+      <c r="I256">
+        <v>1018</v>
+      </c>
+      <c r="J256" t="s">
+        <v>56</v>
+      </c>
+      <c r="K256">
+        <v>60000</v>
+      </c>
+      <c r="L256">
+        <v>60000</v>
+      </c>
+      <c r="M256">
+        <v>24</v>
+      </c>
+      <c r="N256">
+        <v>5</v>
+      </c>
+      <c r="O256" t="s">
+        <v>907</v>
+      </c>
+      <c r="P256">
+        <v>60000</v>
+      </c>
+      <c r="Q256">
+        <v>60000</v>
+      </c>
+      <c r="R256" t="s">
+        <v>58</v>
+      </c>
+      <c r="S256">
+        <v>10</v>
+      </c>
+      <c r="T256">
+        <v>14</v>
+      </c>
+      <c r="U256">
+        <v>1</v>
+      </c>
+      <c r="V256">
+        <v>14</v>
+      </c>
+      <c r="W256" t="s">
+        <v>90</v>
+      </c>
+      <c r="X256" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y256" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z256" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA256" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB256" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC256" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD256" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE256" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF256" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG256">
+        <v>-30</v>
+      </c>
+      <c r="AH256">
+        <v>0</v>
+      </c>
+      <c r="AI256">
+        <v>0</v>
+      </c>
+      <c r="AJ256" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK256" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL256" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM256">
+        <v>973577</v>
+      </c>
+      <c r="AN256">
+        <v>134129</v>
+      </c>
+      <c r="AS256" t="s">
+        <v>140</v>
+      </c>
+      <c r="AT256" t="s">
+        <v>936</v>
+      </c>
+      <c r="AU256" t="s">
+        <v>937</v>
+      </c>
+      <c r="AV256" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="257" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>48</v>
+      </c>
+      <c r="B257" t="s">
+        <v>163</v>
+      </c>
+      <c r="C257" t="s">
+        <v>939</v>
+      </c>
+      <c r="D257" t="s">
+        <v>940</v>
+      </c>
+      <c r="E257" t="s">
+        <v>941</v>
+      </c>
+      <c r="F257" t="s">
+        <v>53</v>
+      </c>
+      <c r="G257" t="s">
+        <v>147</v>
+      </c>
+      <c r="H257" t="s">
+        <v>108</v>
+      </c>
+      <c r="I257">
+        <v>1383</v>
+      </c>
+      <c r="J257" t="s">
+        <v>56</v>
+      </c>
+      <c r="K257">
+        <v>28646</v>
+      </c>
+      <c r="L257">
+        <v>28646</v>
+      </c>
+      <c r="M257">
+        <v>60</v>
+      </c>
+      <c r="N257">
+        <v>5</v>
+      </c>
+      <c r="O257" t="s">
+        <v>907</v>
+      </c>
+      <c r="P257">
+        <v>28646</v>
+      </c>
+      <c r="Q257">
+        <v>28646</v>
+      </c>
+      <c r="R257" t="s">
+        <v>58</v>
+      </c>
+      <c r="S257">
+        <v>49</v>
+      </c>
+      <c r="T257">
+        <v>11</v>
+      </c>
+      <c r="U257">
+        <v>1</v>
+      </c>
+      <c r="V257">
+        <v>11</v>
+      </c>
+      <c r="W257" t="s">
+        <v>90</v>
+      </c>
+      <c r="X257" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y257" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z257" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA257" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB257" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC257" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD257" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE257" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF257" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG257">
+        <v>-30</v>
+      </c>
+      <c r="AH257">
+        <v>0</v>
+      </c>
+      <c r="AI257">
+        <v>0</v>
+      </c>
+      <c r="AJ257" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK257" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL257" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM257">
+        <v>973578</v>
+      </c>
+      <c r="AN257">
+        <v>134332</v>
+      </c>
+      <c r="AS257" t="s">
+        <v>99</v>
+      </c>
+      <c r="AT257" t="s">
+        <v>942</v>
+      </c>
+      <c r="AU257" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV257" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="258" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>48</v>
+      </c>
+      <c r="B258" t="s">
+        <v>163</v>
+      </c>
+      <c r="C258" t="s">
+        <v>414</v>
+      </c>
+      <c r="D258" t="s">
+        <v>944</v>
+      </c>
+      <c r="E258" t="s">
+        <v>945</v>
+      </c>
+      <c r="F258" t="s">
+        <v>53</v>
+      </c>
+      <c r="G258" t="s">
+        <v>75</v>
+      </c>
+      <c r="H258" t="s">
+        <v>108</v>
+      </c>
+      <c r="I258">
+        <v>1455</v>
+      </c>
+      <c r="J258" t="s">
+        <v>56</v>
+      </c>
+      <c r="K258">
+        <v>29167</v>
+      </c>
+      <c r="L258">
+        <v>29167</v>
+      </c>
+      <c r="M258">
+        <v>60</v>
+      </c>
+      <c r="N258">
+        <v>5</v>
+      </c>
+      <c r="O258" t="s">
+        <v>907</v>
+      </c>
+      <c r="P258">
+        <v>29167</v>
+      </c>
+      <c r="Q258">
+        <v>29167</v>
+      </c>
+      <c r="R258" t="s">
+        <v>58</v>
+      </c>
+      <c r="S258">
+        <v>49</v>
+      </c>
+      <c r="T258">
+        <v>11</v>
+      </c>
+      <c r="U258">
+        <v>1</v>
+      </c>
+      <c r="V258">
+        <v>11</v>
+      </c>
+      <c r="W258" t="s">
+        <v>90</v>
+      </c>
+      <c r="X258" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y258" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z258" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA258" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB258" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC258" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD258" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE258" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF258" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG258">
+        <v>-30</v>
+      </c>
+      <c r="AH258">
+        <v>0</v>
+      </c>
+      <c r="AI258">
+        <v>0</v>
+      </c>
+      <c r="AJ258" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK258" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL258" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM258">
+        <v>973579</v>
+      </c>
+      <c r="AN258">
+        <v>134357</v>
+      </c>
+      <c r="AS258" t="s">
+        <v>140</v>
+      </c>
+      <c r="AT258" t="s">
+        <v>946</v>
+      </c>
+      <c r="AV258" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="259" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>48</v>
+      </c>
+      <c r="B259" t="s">
+        <v>948</v>
+      </c>
+      <c r="C259" t="s">
+        <v>949</v>
+      </c>
+      <c r="D259" t="s">
+        <v>950</v>
+      </c>
+      <c r="E259" t="s">
+        <v>951</v>
+      </c>
+      <c r="F259" t="s">
+        <v>53</v>
+      </c>
+      <c r="G259" t="s">
+        <v>160</v>
+      </c>
+      <c r="H259" t="s">
+        <v>108</v>
+      </c>
+      <c r="I259">
+        <v>1501</v>
+      </c>
+      <c r="J259" t="s">
+        <v>56</v>
+      </c>
+      <c r="K259">
+        <v>66667</v>
+      </c>
+      <c r="L259">
+        <v>66667</v>
+      </c>
+      <c r="M259">
+        <v>36</v>
+      </c>
+      <c r="N259">
+        <v>5</v>
+      </c>
+      <c r="O259" t="s">
+        <v>907</v>
+      </c>
+      <c r="P259">
+        <v>66667</v>
+      </c>
+      <c r="Q259">
+        <v>66667</v>
+      </c>
+      <c r="R259" t="s">
+        <v>58</v>
+      </c>
+      <c r="S259">
+        <v>26</v>
+      </c>
+      <c r="T259">
+        <v>10</v>
+      </c>
+      <c r="U259">
+        <v>1</v>
+      </c>
+      <c r="V259">
+        <v>10</v>
+      </c>
+      <c r="W259" t="s">
+        <v>90</v>
+      </c>
+      <c r="X259" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y259" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z259" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA259" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB259" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC259" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD259" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE259" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF259" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG259">
+        <v>-30</v>
+      </c>
+      <c r="AH259">
+        <v>0</v>
+      </c>
+      <c r="AI259">
+        <v>0</v>
+      </c>
+      <c r="AJ259" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK259" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL259" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM259">
+        <v>973580</v>
+      </c>
+      <c r="AN259">
+        <v>134388</v>
+      </c>
+      <c r="AS259" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT259" t="s">
+        <v>952</v>
+      </c>
+      <c r="AU259" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV259" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="260" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>48</v>
+      </c>
+      <c r="B260" t="s">
+        <v>800</v>
+      </c>
+      <c r="C260" t="s">
+        <v>954</v>
+      </c>
+      <c r="D260" t="s">
+        <v>955</v>
+      </c>
+      <c r="E260" t="s">
+        <v>956</v>
+      </c>
+      <c r="F260" t="s">
+        <v>53</v>
+      </c>
+      <c r="G260" t="s">
+        <v>957</v>
+      </c>
+      <c r="H260" t="s">
+        <v>108</v>
+      </c>
+      <c r="I260">
+        <v>2144</v>
+      </c>
+      <c r="J260" t="s">
+        <v>56</v>
+      </c>
+      <c r="K260">
+        <v>62500</v>
+      </c>
+      <c r="L260">
+        <v>62500</v>
+      </c>
+      <c r="M260">
+        <v>24</v>
+      </c>
+      <c r="N260">
+        <v>5</v>
+      </c>
+      <c r="O260" t="s">
+        <v>907</v>
+      </c>
+      <c r="P260">
+        <v>62500</v>
+      </c>
+      <c r="Q260">
+        <v>62500</v>
+      </c>
+      <c r="R260" t="s">
+        <v>58</v>
+      </c>
+      <c r="S260">
+        <v>17</v>
+      </c>
+      <c r="T260">
+        <v>7</v>
+      </c>
+      <c r="U260">
+        <v>1</v>
+      </c>
+      <c r="V260">
+        <v>7</v>
+      </c>
+      <c r="W260" t="s">
+        <v>7</v>
+      </c>
+      <c r="X260" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y260" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z260" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA260" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB260" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD260" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE260" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF260" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG260">
+        <v>-30</v>
+      </c>
+      <c r="AH260">
+        <v>0</v>
+      </c>
+      <c r="AI260">
+        <v>0</v>
+      </c>
+      <c r="AJ260" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK260" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL260" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM260">
+        <v>973581</v>
+      </c>
+      <c r="AN260">
+        <v>134694</v>
+      </c>
+      <c r="AS260" t="s">
+        <v>140</v>
+      </c>
+      <c r="AT260" t="s">
+        <v>958</v>
+      </c>
+      <c r="AU260" t="s">
+        <v>959</v>
+      </c>
+      <c r="AV260" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="261" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>48</v>
+      </c>
+      <c r="B261" t="s">
+        <v>296</v>
+      </c>
+      <c r="C261" t="s">
+        <v>954</v>
+      </c>
+      <c r="D261" t="s">
+        <v>960</v>
+      </c>
+      <c r="E261" t="s">
+        <v>961</v>
+      </c>
+      <c r="F261" t="s">
+        <v>53</v>
+      </c>
+      <c r="G261" t="s">
+        <v>287</v>
+      </c>
+      <c r="H261" t="s">
+        <v>108</v>
+      </c>
+      <c r="I261">
+        <v>2152</v>
+      </c>
+      <c r="J261" t="s">
+        <v>56</v>
+      </c>
+      <c r="K261">
+        <v>102917</v>
+      </c>
+      <c r="L261">
+        <v>102917</v>
+      </c>
+      <c r="M261">
+        <v>24</v>
+      </c>
+      <c r="N261">
+        <v>5</v>
+      </c>
+      <c r="O261" t="s">
+        <v>907</v>
+      </c>
+      <c r="P261">
+        <v>102917</v>
+      </c>
+      <c r="Q261">
+        <v>102917</v>
+      </c>
+      <c r="R261" t="s">
+        <v>58</v>
+      </c>
+      <c r="S261">
+        <v>17</v>
+      </c>
+      <c r="T261">
+        <v>7</v>
+      </c>
+      <c r="U261">
+        <v>1</v>
+      </c>
+      <c r="V261">
+        <v>7</v>
+      </c>
+      <c r="W261" t="s">
+        <v>90</v>
+      </c>
+      <c r="X261" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y261" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z261" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA261" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB261" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD261" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE261" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF261" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG261">
+        <v>-30</v>
+      </c>
+      <c r="AH261">
+        <v>0</v>
+      </c>
+      <c r="AI261">
+        <v>0</v>
+      </c>
+      <c r="AJ261" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK261" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL261" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM261">
+        <v>973582</v>
+      </c>
+      <c r="AN261">
+        <v>134696</v>
+      </c>
+      <c r="AS261" t="s">
+        <v>99</v>
+      </c>
+      <c r="AT261" t="s">
+        <v>962</v>
+      </c>
+      <c r="AU261" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV261" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="262" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>48</v>
+      </c>
+      <c r="B262" t="s">
+        <v>736</v>
+      </c>
+      <c r="C262" t="s">
+        <v>964</v>
+      </c>
+      <c r="D262" t="s">
+        <v>965</v>
+      </c>
+      <c r="E262" t="s">
+        <v>966</v>
+      </c>
+      <c r="F262" t="s">
+        <v>53</v>
+      </c>
+      <c r="G262" t="s">
+        <v>529</v>
+      </c>
+      <c r="H262" t="s">
+        <v>108</v>
+      </c>
+      <c r="I262">
+        <v>2256</v>
+      </c>
+      <c r="J262" t="s">
+        <v>56</v>
+      </c>
+      <c r="K262">
+        <v>40000</v>
+      </c>
+      <c r="L262">
+        <v>40000</v>
+      </c>
+      <c r="M262">
+        <v>36</v>
+      </c>
+      <c r="N262">
+        <v>5</v>
+      </c>
+      <c r="O262" t="s">
+        <v>907</v>
+      </c>
+      <c r="P262">
+        <v>40000</v>
+      </c>
+      <c r="Q262">
+        <v>40000</v>
+      </c>
+      <c r="R262" t="s">
+        <v>58</v>
+      </c>
+      <c r="S262">
+        <v>29</v>
+      </c>
+      <c r="T262">
+        <v>7</v>
+      </c>
+      <c r="U262">
+        <v>1</v>
+      </c>
+      <c r="V262">
+        <v>7</v>
+      </c>
+      <c r="W262" t="s">
+        <v>90</v>
+      </c>
+      <c r="X262" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y262" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z262" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA262" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB262" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD262" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE262" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF262" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG262">
+        <v>-30</v>
+      </c>
+      <c r="AH262">
+        <v>0</v>
+      </c>
+      <c r="AI262">
+        <v>0</v>
+      </c>
+      <c r="AJ262" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK262" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL262" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM262">
+        <v>973583</v>
+      </c>
+      <c r="AN262">
+        <v>134717</v>
+      </c>
+      <c r="AS262" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT262" t="s">
+        <v>967</v>
+      </c>
+      <c r="AU262" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV262" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="263" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>48</v>
+      </c>
+      <c r="B263" t="s">
+        <v>969</v>
+      </c>
+      <c r="C263" t="s">
+        <v>887</v>
+      </c>
+      <c r="D263" t="s">
+        <v>970</v>
+      </c>
+      <c r="E263" t="s">
+        <v>971</v>
+      </c>
+      <c r="F263" t="s">
+        <v>53</v>
+      </c>
+      <c r="G263" t="s">
+        <v>147</v>
+      </c>
+      <c r="H263" t="s">
+        <v>108</v>
+      </c>
+      <c r="I263">
+        <v>2419</v>
+      </c>
+      <c r="J263" t="s">
+        <v>56</v>
+      </c>
+      <c r="K263">
+        <v>47717</v>
+      </c>
+      <c r="L263">
+        <v>47717</v>
+      </c>
+      <c r="M263">
+        <v>47</v>
+      </c>
+      <c r="N263">
+        <v>5</v>
+      </c>
+      <c r="O263" t="s">
+        <v>907</v>
+      </c>
+      <c r="P263">
+        <v>47717</v>
+      </c>
+      <c r="Q263">
+        <v>47717</v>
+      </c>
+      <c r="R263" t="s">
+        <v>58</v>
+      </c>
+      <c r="S263">
+        <v>40</v>
+      </c>
+      <c r="T263">
+        <v>7</v>
+      </c>
+      <c r="U263">
+        <v>1</v>
+      </c>
+      <c r="V263">
+        <v>7</v>
+      </c>
+      <c r="W263" t="s">
+        <v>90</v>
+      </c>
+      <c r="X263" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y263" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z263" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA263" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB263" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD263" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE263" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF263" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG263">
+        <v>-30</v>
+      </c>
+      <c r="AH263">
+        <v>0</v>
+      </c>
+      <c r="AI263">
+        <v>0</v>
+      </c>
+      <c r="AJ263" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK263" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL263" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM263">
+        <v>973584</v>
+      </c>
+      <c r="AN263">
+        <v>134757</v>
+      </c>
+      <c r="AS263" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT263" t="s">
+        <v>972</v>
+      </c>
+      <c r="AU263" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV263" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="264" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>48</v>
+      </c>
+      <c r="B264" t="s">
+        <v>322</v>
+      </c>
+      <c r="C264" t="s">
+        <v>974</v>
+      </c>
+      <c r="D264" t="s">
+        <v>975</v>
+      </c>
+      <c r="E264" t="s">
+        <v>976</v>
+      </c>
+      <c r="F264" t="s">
+        <v>53</v>
+      </c>
+      <c r="G264" t="s">
+        <v>392</v>
+      </c>
+      <c r="H264" t="s">
+        <v>108</v>
+      </c>
+      <c r="I264">
+        <v>2684</v>
+      </c>
+      <c r="J264" t="s">
+        <v>56</v>
+      </c>
+      <c r="K264">
+        <v>50000</v>
+      </c>
+      <c r="L264">
+        <v>50000</v>
+      </c>
+      <c r="M264">
+        <v>30</v>
+      </c>
+      <c r="N264">
+        <v>5</v>
+      </c>
+      <c r="O264" t="s">
+        <v>907</v>
+      </c>
+      <c r="P264">
+        <v>50000</v>
+      </c>
+      <c r="Q264">
+        <v>50000</v>
+      </c>
+      <c r="R264" t="s">
+        <v>58</v>
+      </c>
+      <c r="S264">
+        <v>24</v>
+      </c>
+      <c r="T264">
+        <v>6</v>
+      </c>
+      <c r="U264">
+        <v>1</v>
+      </c>
+      <c r="V264">
+        <v>6</v>
+      </c>
+      <c r="W264" t="s">
+        <v>90</v>
+      </c>
+      <c r="X264" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y264" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z264" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA264" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB264" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD264" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE264" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF264" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG264">
+        <v>-30</v>
+      </c>
+      <c r="AH264">
+        <v>0</v>
+      </c>
+      <c r="AI264">
+        <v>0</v>
+      </c>
+      <c r="AJ264" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK264" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL264" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM264">
+        <v>973585</v>
+      </c>
+      <c r="AN264">
+        <v>134841</v>
+      </c>
+      <c r="AS264" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT264" t="s">
+        <v>977</v>
+      </c>
+      <c r="AU264" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV264" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="265" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>48</v>
+      </c>
+      <c r="B265" t="s">
+        <v>322</v>
+      </c>
+      <c r="C265" t="s">
+        <v>974</v>
+      </c>
+      <c r="D265" t="s">
+        <v>979</v>
+      </c>
+      <c r="E265" t="s">
+        <v>980</v>
+      </c>
+      <c r="F265" t="s">
+        <v>53</v>
+      </c>
+      <c r="G265" t="s">
+        <v>392</v>
+      </c>
+      <c r="H265" t="s">
+        <v>108</v>
+      </c>
+      <c r="I265">
+        <v>2686</v>
+      </c>
+      <c r="J265" t="s">
+        <v>56</v>
+      </c>
+      <c r="K265">
+        <v>50000</v>
+      </c>
+      <c r="L265">
+        <v>50000</v>
+      </c>
+      <c r="M265">
+        <v>30</v>
+      </c>
+      <c r="N265">
+        <v>5</v>
+      </c>
+      <c r="O265" t="s">
+        <v>907</v>
+      </c>
+      <c r="P265">
+        <v>50000</v>
+      </c>
+      <c r="Q265">
+        <v>50000</v>
+      </c>
+      <c r="R265" t="s">
+        <v>58</v>
+      </c>
+      <c r="S265">
+        <v>24</v>
+      </c>
+      <c r="T265">
+        <v>6</v>
+      </c>
+      <c r="U265">
+        <v>1</v>
+      </c>
+      <c r="V265">
+        <v>6</v>
+      </c>
+      <c r="W265" t="s">
+        <v>90</v>
+      </c>
+      <c r="X265" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y265" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z265" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA265" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB265" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD265" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE265" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF265" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG265">
+        <v>-30</v>
+      </c>
+      <c r="AH265">
+        <v>0</v>
+      </c>
+      <c r="AI265">
+        <v>0</v>
+      </c>
+      <c r="AJ265" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK265" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL265" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM265">
+        <v>973586</v>
+      </c>
+      <c r="AN265">
+        <v>134842</v>
+      </c>
+      <c r="AS265" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT265" t="s">
+        <v>981</v>
+      </c>
+      <c r="AU265" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV265" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="266" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>48</v>
+      </c>
+      <c r="B266" t="s">
+        <v>754</v>
+      </c>
+      <c r="C266" t="s">
+        <v>850</v>
+      </c>
+      <c r="D266" t="s">
+        <v>983</v>
+      </c>
+      <c r="E266" t="s">
+        <v>984</v>
+      </c>
+      <c r="F266" t="s">
+        <v>53</v>
+      </c>
+      <c r="G266" t="s">
+        <v>198</v>
+      </c>
+      <c r="H266" t="s">
+        <v>782</v>
+      </c>
+      <c r="I266">
+        <v>2858</v>
+      </c>
+      <c r="J266" t="s">
+        <v>56</v>
+      </c>
+      <c r="K266">
+        <v>56250</v>
+      </c>
+      <c r="L266">
+        <v>56250</v>
+      </c>
+      <c r="M266">
+        <v>24</v>
+      </c>
+      <c r="N266">
+        <v>5</v>
+      </c>
+      <c r="O266" t="s">
+        <v>907</v>
+      </c>
+      <c r="P266">
+        <v>56250</v>
+      </c>
+      <c r="Q266">
+        <v>56250</v>
+      </c>
+      <c r="R266" t="s">
+        <v>58</v>
+      </c>
+      <c r="S266">
+        <v>20</v>
+      </c>
+      <c r="T266">
+        <v>4</v>
+      </c>
+      <c r="U266">
+        <v>1</v>
+      </c>
+      <c r="V266">
+        <v>4</v>
+      </c>
+      <c r="W266" t="s">
+        <v>7</v>
+      </c>
+      <c r="X266" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y266" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z266" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA266" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB266" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD266" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE266" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF266" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG266">
+        <v>-30</v>
+      </c>
+      <c r="AH266">
+        <v>0</v>
+      </c>
+      <c r="AI266">
+        <v>0</v>
+      </c>
+      <c r="AJ266" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK266" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL266" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM266">
+        <v>973587</v>
+      </c>
+      <c r="AN266">
+        <v>134883</v>
+      </c>
+      <c r="AS266" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT266" t="s">
+        <v>985</v>
+      </c>
+      <c r="AU266" t="s">
+        <v>986</v>
+      </c>
+      <c r="AV266" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="267" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>48</v>
+      </c>
+      <c r="B267" t="s">
+        <v>754</v>
+      </c>
+      <c r="C267" t="s">
+        <v>850</v>
+      </c>
+      <c r="D267" t="s">
+        <v>983</v>
+      </c>
+      <c r="E267" t="s">
+        <v>984</v>
+      </c>
+      <c r="F267" t="s">
+        <v>53</v>
+      </c>
+      <c r="G267" t="s">
+        <v>198</v>
+      </c>
+      <c r="H267" t="s">
+        <v>466</v>
+      </c>
+      <c r="I267">
+        <v>2876</v>
+      </c>
+      <c r="J267" t="s">
+        <v>56</v>
+      </c>
+      <c r="K267">
+        <v>53125</v>
+      </c>
+      <c r="L267">
+        <v>53125</v>
+      </c>
+      <c r="M267">
+        <v>24</v>
+      </c>
+      <c r="N267">
+        <v>5</v>
+      </c>
+      <c r="O267" t="s">
+        <v>907</v>
+      </c>
+      <c r="P267">
+        <v>53125</v>
+      </c>
+      <c r="Q267">
+        <v>53125</v>
+      </c>
+      <c r="R267" t="s">
+        <v>58</v>
+      </c>
+      <c r="S267">
+        <v>19</v>
+      </c>
+      <c r="T267">
+        <v>5</v>
+      </c>
+      <c r="U267">
+        <v>1</v>
+      </c>
+      <c r="V267">
+        <v>5</v>
+      </c>
+      <c r="W267" t="s">
+        <v>90</v>
+      </c>
+      <c r="X267" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y267" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z267" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA267" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB267" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD267" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE267" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF267" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG267">
+        <v>-30</v>
+      </c>
+      <c r="AH267">
+        <v>0</v>
+      </c>
+      <c r="AI267">
+        <v>0</v>
+      </c>
+      <c r="AJ267" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK267" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL267" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM267">
+        <v>973588</v>
+      </c>
+      <c r="AN267">
+        <v>134888</v>
+      </c>
+      <c r="AS267" t="s">
+        <v>191</v>
+      </c>
+      <c r="AT267" t="s">
+        <v>985</v>
+      </c>
+      <c r="AU267" t="s">
+        <v>986</v>
+      </c>
+      <c r="AV267" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="268" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>48</v>
+      </c>
+      <c r="B268" t="s">
+        <v>754</v>
+      </c>
+      <c r="C268" t="s">
+        <v>850</v>
+      </c>
+      <c r="D268" t="s">
+        <v>983</v>
+      </c>
+      <c r="E268" t="s">
+        <v>984</v>
+      </c>
+      <c r="F268" t="s">
+        <v>53</v>
+      </c>
+      <c r="G268" t="s">
+        <v>198</v>
+      </c>
+      <c r="H268" t="s">
+        <v>108</v>
+      </c>
+      <c r="I268">
+        <v>2877</v>
+      </c>
+      <c r="J268" t="s">
+        <v>56</v>
+      </c>
+      <c r="K268">
+        <v>64063</v>
+      </c>
+      <c r="L268">
+        <v>64063</v>
+      </c>
+      <c r="M268">
+        <v>24</v>
+      </c>
+      <c r="N268">
+        <v>5</v>
+      </c>
+      <c r="O268" t="s">
+        <v>907</v>
+      </c>
+      <c r="P268">
+        <v>64063</v>
+      </c>
+      <c r="Q268">
+        <v>64063</v>
+      </c>
+      <c r="R268" t="s">
+        <v>58</v>
+      </c>
+      <c r="S268">
+        <v>19</v>
+      </c>
+      <c r="T268">
+        <v>5</v>
+      </c>
+      <c r="U268">
+        <v>1</v>
+      </c>
+      <c r="V268">
+        <v>5</v>
+      </c>
+      <c r="W268" t="s">
+        <v>90</v>
+      </c>
+      <c r="X268" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y268" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z268" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA268" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB268" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD268" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE268" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF268" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG268">
+        <v>-30</v>
+      </c>
+      <c r="AH268">
+        <v>0</v>
+      </c>
+      <c r="AI268">
+        <v>0</v>
+      </c>
+      <c r="AJ268" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK268" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL268" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM268">
+        <v>973589</v>
+      </c>
+      <c r="AN268">
+        <v>134889</v>
+      </c>
+      <c r="AS268" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT268" t="s">
+        <v>985</v>
+      </c>
+      <c r="AU268" t="s">
+        <v>986</v>
+      </c>
+      <c r="AV268" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="269" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>48</v>
+      </c>
+      <c r="B269" t="s">
+        <v>987</v>
+      </c>
+      <c r="C269" t="s">
+        <v>310</v>
+      </c>
+      <c r="D269" t="s">
+        <v>988</v>
+      </c>
+      <c r="E269" t="s">
+        <v>989</v>
+      </c>
+      <c r="F269" t="s">
+        <v>53</v>
+      </c>
+      <c r="G269" t="s">
+        <v>160</v>
+      </c>
+      <c r="H269" t="s">
+        <v>108</v>
+      </c>
+      <c r="I269">
+        <v>3086</v>
+      </c>
+      <c r="J269" t="s">
+        <v>56</v>
+      </c>
+      <c r="K269">
+        <v>28500</v>
+      </c>
+      <c r="L269">
+        <v>28500</v>
+      </c>
+      <c r="M269">
+        <v>60</v>
+      </c>
+      <c r="N269">
+        <v>5</v>
+      </c>
+      <c r="O269" t="s">
+        <v>907</v>
+      </c>
+      <c r="P269">
+        <v>28500</v>
+      </c>
+      <c r="Q269">
+        <v>28500</v>
+      </c>
+      <c r="R269" t="s">
+        <v>58</v>
+      </c>
+      <c r="S269">
+        <v>55</v>
+      </c>
+      <c r="T269">
+        <v>5</v>
+      </c>
+      <c r="U269">
+        <v>1</v>
+      </c>
+      <c r="V269">
+        <v>5</v>
+      </c>
+      <c r="W269" t="s">
+        <v>90</v>
+      </c>
+      <c r="X269" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y269" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z269" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA269" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB269" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD269" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE269" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF269" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG269">
+        <v>-30</v>
+      </c>
+      <c r="AH269">
+        <v>0</v>
+      </c>
+      <c r="AI269">
+        <v>0</v>
+      </c>
+      <c r="AJ269" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK269" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL269" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM269">
+        <v>973590</v>
+      </c>
+      <c r="AN269">
+        <v>134965</v>
+      </c>
+      <c r="AS269" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT269" t="s">
+        <v>990</v>
+      </c>
+      <c r="AU269" t="s">
+        <v>991</v>
+      </c>
+      <c r="AV269" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="270" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>48</v>
+      </c>
+      <c r="B270" t="s">
+        <v>992</v>
+      </c>
+      <c r="C270" t="s">
+        <v>993</v>
+      </c>
+      <c r="D270" t="s">
+        <v>994</v>
+      </c>
+      <c r="E270" t="s">
+        <v>995</v>
+      </c>
+      <c r="F270" t="s">
+        <v>53</v>
+      </c>
+      <c r="G270" t="s">
+        <v>198</v>
+      </c>
+      <c r="H270" t="s">
+        <v>108</v>
+      </c>
+      <c r="I270">
+        <v>3571</v>
+      </c>
+      <c r="J270" t="s">
+        <v>56</v>
+      </c>
+      <c r="K270">
+        <v>33750</v>
+      </c>
+      <c r="L270">
+        <v>33750</v>
+      </c>
+      <c r="M270">
+        <v>48</v>
+      </c>
+      <c r="N270">
+        <v>3</v>
+      </c>
+      <c r="O270" t="s">
+        <v>907</v>
+      </c>
+      <c r="P270">
+        <v>33750</v>
+      </c>
+      <c r="Q270">
+        <v>33750</v>
+      </c>
+      <c r="R270" t="s">
+        <v>58</v>
+      </c>
+      <c r="S270">
+        <v>46</v>
+      </c>
+      <c r="T270">
+        <v>2</v>
+      </c>
+      <c r="U270">
+        <v>1</v>
+      </c>
+      <c r="V270">
+        <v>2</v>
+      </c>
+      <c r="W270" t="s">
+        <v>7</v>
+      </c>
+      <c r="X270" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y270" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z270" t="s">
+        <v>404</v>
+      </c>
+      <c r="AA270" t="s">
+        <v>404</v>
+      </c>
+      <c r="AB270" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD270" t="s">
+        <v>405</v>
+      </c>
+      <c r="AE270" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF270" t="s">
+        <v>379</v>
+      </c>
+      <c r="AG270">
+        <v>2</v>
+      </c>
+      <c r="AH270">
+        <v>0</v>
+      </c>
+      <c r="AI270">
+        <v>0</v>
+      </c>
+      <c r="AJ270" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK270" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL270" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM270">
+        <v>973592</v>
+      </c>
+      <c r="AN270">
+        <v>135097</v>
+      </c>
+      <c r="AS270" t="s">
+        <v>140</v>
+      </c>
+      <c r="AT270" t="s">
+        <v>996</v>
+      </c>
+      <c r="AU270" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV270" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="271" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>48</v>
+      </c>
+      <c r="B271" t="s">
+        <v>998</v>
+      </c>
+      <c r="C271" t="s">
+        <v>284</v>
+      </c>
+      <c r="D271" t="s">
+        <v>999</v>
+      </c>
+      <c r="E271" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F271" t="s">
+        <v>53</v>
+      </c>
+      <c r="G271" t="s">
+        <v>442</v>
+      </c>
+      <c r="H271" t="s">
+        <v>108</v>
+      </c>
+      <c r="I271">
+        <v>4639</v>
+      </c>
+      <c r="J271" t="s">
+        <v>56</v>
+      </c>
+      <c r="K271">
+        <v>118125</v>
+      </c>
+      <c r="L271">
+        <v>118125</v>
+      </c>
+      <c r="M271">
+        <v>24</v>
+      </c>
+      <c r="N271">
+        <v>16</v>
+      </c>
+      <c r="O271" t="s">
+        <v>907</v>
+      </c>
+      <c r="P271">
+        <v>118125</v>
+      </c>
+      <c r="Q271">
+        <v>118125</v>
+      </c>
+      <c r="R271" t="s">
+        <v>58</v>
+      </c>
+      <c r="S271">
+        <v>12</v>
+      </c>
+      <c r="T271">
+        <v>12</v>
+      </c>
+      <c r="U271">
+        <v>1</v>
+      </c>
+      <c r="V271">
+        <v>1</v>
+      </c>
+      <c r="W271" t="s">
+        <v>90</v>
+      </c>
+      <c r="X271" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y271" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z271" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA271" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB271" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD271" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE271" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF271" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG271">
+        <v>-406</v>
+      </c>
+      <c r="AH271">
+        <v>0</v>
+      </c>
+      <c r="AI271">
+        <v>0</v>
+      </c>
+      <c r="AJ271" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK271" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AL271" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM271">
+        <v>973593</v>
+      </c>
+      <c r="AN271">
+        <v>135464</v>
+      </c>
+      <c r="AS271" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT271" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AU271" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV271" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="272" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>48</v>
+      </c>
+      <c r="B272" t="s">
+        <v>998</v>
+      </c>
+      <c r="C272" t="s">
+        <v>284</v>
+      </c>
+      <c r="D272" t="s">
+        <v>999</v>
+      </c>
+      <c r="E272" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F272" t="s">
+        <v>53</v>
+      </c>
+      <c r="G272" t="s">
+        <v>442</v>
+      </c>
+      <c r="H272" t="s">
+        <v>108</v>
+      </c>
+      <c r="I272">
+        <v>4639</v>
+      </c>
+      <c r="J272" t="s">
+        <v>56</v>
+      </c>
+      <c r="K272">
+        <v>118125</v>
+      </c>
+      <c r="L272">
+        <v>118125</v>
+      </c>
+      <c r="M272">
+        <v>24</v>
+      </c>
+      <c r="N272">
+        <v>16</v>
+      </c>
+      <c r="O272" t="s">
+        <v>907</v>
+      </c>
+      <c r="P272">
+        <v>118125</v>
+      </c>
+      <c r="Q272">
+        <v>118125</v>
+      </c>
+      <c r="R272" t="s">
+        <v>58</v>
+      </c>
+      <c r="S272">
+        <v>12</v>
+      </c>
+      <c r="T272">
+        <v>12</v>
+      </c>
+      <c r="U272">
+        <v>1</v>
+      </c>
+      <c r="V272">
+        <v>2</v>
+      </c>
+      <c r="W272" t="s">
+        <v>90</v>
+      </c>
+      <c r="X272" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y272" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z272" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA272" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB272" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD272" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE272" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF272" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG272">
+        <v>-406</v>
+      </c>
+      <c r="AH272">
+        <v>0</v>
+      </c>
+      <c r="AI272">
+        <v>0</v>
+      </c>
+      <c r="AJ272" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK272" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AL272" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM272">
+        <v>973593</v>
+      </c>
+      <c r="AN272">
+        <v>135464</v>
+      </c>
+      <c r="AS272" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT272" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AU272" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV272" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="273" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>48</v>
+      </c>
+      <c r="B273" t="s">
+        <v>998</v>
+      </c>
+      <c r="C273" t="s">
+        <v>284</v>
+      </c>
+      <c r="D273" t="s">
+        <v>999</v>
+      </c>
+      <c r="E273" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F273" t="s">
+        <v>53</v>
+      </c>
+      <c r="G273" t="s">
+        <v>442</v>
+      </c>
+      <c r="H273" t="s">
+        <v>108</v>
+      </c>
+      <c r="I273">
+        <v>4639</v>
+      </c>
+      <c r="J273" t="s">
+        <v>56</v>
+      </c>
+      <c r="K273">
+        <v>118125</v>
+      </c>
+      <c r="L273">
+        <v>118125</v>
+      </c>
+      <c r="M273">
+        <v>24</v>
+      </c>
+      <c r="N273">
+        <v>16</v>
+      </c>
+      <c r="O273" t="s">
+        <v>907</v>
+      </c>
+      <c r="P273">
+        <v>118125</v>
+      </c>
+      <c r="Q273">
+        <v>118125</v>
+      </c>
+      <c r="R273" t="s">
+        <v>58</v>
+      </c>
+      <c r="S273">
+        <v>12</v>
+      </c>
+      <c r="T273">
+        <v>12</v>
+      </c>
+      <c r="U273">
+        <v>1</v>
+      </c>
+      <c r="V273">
+        <v>3</v>
+      </c>
+      <c r="W273" t="s">
+        <v>90</v>
+      </c>
+      <c r="X273" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y273" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z273" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA273" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB273" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD273" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE273" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF273" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG273">
+        <v>-406</v>
+      </c>
+      <c r="AH273">
+        <v>0</v>
+      </c>
+      <c r="AI273">
+        <v>0</v>
+      </c>
+      <c r="AJ273" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK273" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AL273" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM273">
+        <v>973593</v>
+      </c>
+      <c r="AN273">
+        <v>135464</v>
+      </c>
+      <c r="AS273" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT273" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AU273" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV273" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="274" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>48</v>
+      </c>
+      <c r="B274" t="s">
+        <v>998</v>
+      </c>
+      <c r="C274" t="s">
+        <v>284</v>
+      </c>
+      <c r="D274" t="s">
+        <v>999</v>
+      </c>
+      <c r="E274" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F274" t="s">
+        <v>53</v>
+      </c>
+      <c r="G274" t="s">
+        <v>442</v>
+      </c>
+      <c r="H274" t="s">
+        <v>108</v>
+      </c>
+      <c r="I274">
+        <v>4639</v>
+      </c>
+      <c r="J274" t="s">
+        <v>56</v>
+      </c>
+      <c r="K274">
+        <v>118125</v>
+      </c>
+      <c r="L274">
+        <v>118125</v>
+      </c>
+      <c r="M274">
+        <v>24</v>
+      </c>
+      <c r="N274">
+        <v>16</v>
+      </c>
+      <c r="O274" t="s">
+        <v>907</v>
+      </c>
+      <c r="P274">
+        <v>118125</v>
+      </c>
+      <c r="Q274">
+        <v>118125</v>
+      </c>
+      <c r="R274" t="s">
+        <v>58</v>
+      </c>
+      <c r="S274">
+        <v>12</v>
+      </c>
+      <c r="T274">
+        <v>12</v>
+      </c>
+      <c r="U274">
+        <v>1</v>
+      </c>
+      <c r="V274">
+        <v>4</v>
+      </c>
+      <c r="W274" t="s">
+        <v>90</v>
+      </c>
+      <c r="X274" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y274" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z274" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA274" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB274" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD274" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE274" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF274" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG274">
+        <v>-406</v>
+      </c>
+      <c r="AH274">
+        <v>0</v>
+      </c>
+      <c r="AI274">
+        <v>0</v>
+      </c>
+      <c r="AJ274" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK274" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AL274" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM274">
+        <v>973593</v>
+      </c>
+      <c r="AN274">
+        <v>135464</v>
+      </c>
+      <c r="AS274" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT274" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AU274" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV274" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="275" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>48</v>
+      </c>
+      <c r="B275" t="s">
+        <v>998</v>
+      </c>
+      <c r="C275" t="s">
+        <v>284</v>
+      </c>
+      <c r="D275" t="s">
+        <v>999</v>
+      </c>
+      <c r="E275" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F275" t="s">
+        <v>53</v>
+      </c>
+      <c r="G275" t="s">
+        <v>442</v>
+      </c>
+      <c r="H275" t="s">
+        <v>108</v>
+      </c>
+      <c r="I275">
+        <v>4639</v>
+      </c>
+      <c r="J275" t="s">
+        <v>56</v>
+      </c>
+      <c r="K275">
+        <v>118125</v>
+      </c>
+      <c r="L275">
+        <v>118125</v>
+      </c>
+      <c r="M275">
+        <v>24</v>
+      </c>
+      <c r="N275">
+        <v>16</v>
+      </c>
+      <c r="O275" t="s">
+        <v>907</v>
+      </c>
+      <c r="P275">
+        <v>118125</v>
+      </c>
+      <c r="Q275">
+        <v>118125</v>
+      </c>
+      <c r="R275" t="s">
+        <v>58</v>
+      </c>
+      <c r="S275">
+        <v>12</v>
+      </c>
+      <c r="T275">
+        <v>12</v>
+      </c>
+      <c r="U275">
+        <v>1</v>
+      </c>
+      <c r="V275">
+        <v>5</v>
+      </c>
+      <c r="W275" t="s">
+        <v>90</v>
+      </c>
+      <c r="X275" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y275" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z275" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA275" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB275" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD275" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE275" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF275" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG275">
+        <v>-406</v>
+      </c>
+      <c r="AH275">
+        <v>0</v>
+      </c>
+      <c r="AI275">
+        <v>0</v>
+      </c>
+      <c r="AJ275" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK275" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AL275" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM275">
+        <v>973593</v>
+      </c>
+      <c r="AN275">
+        <v>135464</v>
+      </c>
+      <c r="AS275" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT275" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AU275" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV275" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="276" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>48</v>
+      </c>
+      <c r="B276" t="s">
+        <v>998</v>
+      </c>
+      <c r="C276" t="s">
+        <v>284</v>
+      </c>
+      <c r="D276" t="s">
+        <v>999</v>
+      </c>
+      <c r="E276" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F276" t="s">
+        <v>53</v>
+      </c>
+      <c r="G276" t="s">
+        <v>442</v>
+      </c>
+      <c r="H276" t="s">
+        <v>108</v>
+      </c>
+      <c r="I276">
+        <v>4639</v>
+      </c>
+      <c r="J276" t="s">
+        <v>56</v>
+      </c>
+      <c r="K276">
+        <v>118125</v>
+      </c>
+      <c r="L276">
+        <v>118125</v>
+      </c>
+      <c r="M276">
+        <v>24</v>
+      </c>
+      <c r="N276">
+        <v>16</v>
+      </c>
+      <c r="O276" t="s">
+        <v>907</v>
+      </c>
+      <c r="P276">
+        <v>118125</v>
+      </c>
+      <c r="Q276">
+        <v>118125</v>
+      </c>
+      <c r="R276" t="s">
+        <v>58</v>
+      </c>
+      <c r="S276">
+        <v>12</v>
+      </c>
+      <c r="T276">
+        <v>12</v>
+      </c>
+      <c r="U276">
+        <v>1</v>
+      </c>
+      <c r="V276">
+        <v>6</v>
+      </c>
+      <c r="W276" t="s">
+        <v>90</v>
+      </c>
+      <c r="X276" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y276" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z276" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA276" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB276" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD276" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE276" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF276" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG276">
+        <v>-406</v>
+      </c>
+      <c r="AH276">
+        <v>0</v>
+      </c>
+      <c r="AI276">
+        <v>0</v>
+      </c>
+      <c r="AJ276" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK276" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AL276" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM276">
+        <v>973593</v>
+      </c>
+      <c r="AN276">
+        <v>135464</v>
+      </c>
+      <c r="AS276" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT276" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AU276" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV276" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="277" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>48</v>
+      </c>
+      <c r="B277" t="s">
+        <v>998</v>
+      </c>
+      <c r="C277" t="s">
+        <v>284</v>
+      </c>
+      <c r="D277" t="s">
+        <v>999</v>
+      </c>
+      <c r="E277" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F277" t="s">
+        <v>53</v>
+      </c>
+      <c r="G277" t="s">
+        <v>442</v>
+      </c>
+      <c r="H277" t="s">
+        <v>108</v>
+      </c>
+      <c r="I277">
+        <v>4639</v>
+      </c>
+      <c r="J277" t="s">
+        <v>56</v>
+      </c>
+      <c r="K277">
+        <v>118125</v>
+      </c>
+      <c r="L277">
+        <v>118125</v>
+      </c>
+      <c r="M277">
+        <v>24</v>
+      </c>
+      <c r="N277">
+        <v>16</v>
+      </c>
+      <c r="O277" t="s">
+        <v>907</v>
+      </c>
+      <c r="P277">
+        <v>118125</v>
+      </c>
+      <c r="Q277">
+        <v>118125</v>
+      </c>
+      <c r="R277" t="s">
+        <v>58</v>
+      </c>
+      <c r="S277">
+        <v>12</v>
+      </c>
+      <c r="T277">
+        <v>12</v>
+      </c>
+      <c r="U277">
+        <v>1</v>
+      </c>
+      <c r="V277">
+        <v>7</v>
+      </c>
+      <c r="W277" t="s">
+        <v>90</v>
+      </c>
+      <c r="X277" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y277" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z277" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA277" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB277" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD277" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE277" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF277" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG277">
+        <v>-406</v>
+      </c>
+      <c r="AH277">
+        <v>0</v>
+      </c>
+      <c r="AI277">
+        <v>0</v>
+      </c>
+      <c r="AJ277" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK277" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AL277" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM277">
+        <v>973593</v>
+      </c>
+      <c r="AN277">
+        <v>135464</v>
+      </c>
+      <c r="AS277" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT277" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AU277" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV277" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="278" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>48</v>
+      </c>
+      <c r="B278" t="s">
+        <v>998</v>
+      </c>
+      <c r="C278" t="s">
+        <v>284</v>
+      </c>
+      <c r="D278" t="s">
+        <v>999</v>
+      </c>
+      <c r="E278" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F278" t="s">
+        <v>53</v>
+      </c>
+      <c r="G278" t="s">
+        <v>442</v>
+      </c>
+      <c r="H278" t="s">
+        <v>108</v>
+      </c>
+      <c r="I278">
+        <v>4639</v>
+      </c>
+      <c r="J278" t="s">
+        <v>56</v>
+      </c>
+      <c r="K278">
+        <v>118125</v>
+      </c>
+      <c r="L278">
+        <v>118125</v>
+      </c>
+      <c r="M278">
+        <v>24</v>
+      </c>
+      <c r="N278">
+        <v>16</v>
+      </c>
+      <c r="O278" t="s">
+        <v>907</v>
+      </c>
+      <c r="P278">
+        <v>118125</v>
+      </c>
+      <c r="Q278">
+        <v>118125</v>
+      </c>
+      <c r="R278" t="s">
+        <v>58</v>
+      </c>
+      <c r="S278">
+        <v>12</v>
+      </c>
+      <c r="T278">
+        <v>12</v>
+      </c>
+      <c r="U278">
+        <v>1</v>
+      </c>
+      <c r="V278">
+        <v>8</v>
+      </c>
+      <c r="W278" t="s">
+        <v>90</v>
+      </c>
+      <c r="X278" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y278" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z278" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA278" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB278" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD278" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE278" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF278" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG278">
+        <v>-406</v>
+      </c>
+      <c r="AH278">
+        <v>0</v>
+      </c>
+      <c r="AI278">
+        <v>0</v>
+      </c>
+      <c r="AJ278" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK278" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AL278" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM278">
+        <v>973593</v>
+      </c>
+      <c r="AN278">
+        <v>135464</v>
+      </c>
+      <c r="AS278" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT278" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AU278" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV278" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="279" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>48</v>
+      </c>
+      <c r="B279" t="s">
+        <v>998</v>
+      </c>
+      <c r="C279" t="s">
+        <v>284</v>
+      </c>
+      <c r="D279" t="s">
+        <v>999</v>
+      </c>
+      <c r="E279" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F279" t="s">
+        <v>53</v>
+      </c>
+      <c r="G279" t="s">
+        <v>442</v>
+      </c>
+      <c r="H279" t="s">
+        <v>108</v>
+      </c>
+      <c r="I279">
+        <v>4639</v>
+      </c>
+      <c r="J279" t="s">
+        <v>56</v>
+      </c>
+      <c r="K279">
+        <v>118125</v>
+      </c>
+      <c r="L279">
+        <v>118125</v>
+      </c>
+      <c r="M279">
+        <v>24</v>
+      </c>
+      <c r="N279">
+        <v>16</v>
+      </c>
+      <c r="O279" t="s">
+        <v>907</v>
+      </c>
+      <c r="P279">
+        <v>118125</v>
+      </c>
+      <c r="Q279">
+        <v>118125</v>
+      </c>
+      <c r="R279" t="s">
+        <v>58</v>
+      </c>
+      <c r="S279">
+        <v>12</v>
+      </c>
+      <c r="T279">
+        <v>12</v>
+      </c>
+      <c r="U279">
+        <v>1</v>
+      </c>
+      <c r="V279">
+        <v>9</v>
+      </c>
+      <c r="W279" t="s">
+        <v>90</v>
+      </c>
+      <c r="X279" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y279" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z279" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA279" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB279" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD279" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE279" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF279" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG279">
+        <v>-406</v>
+      </c>
+      <c r="AH279">
+        <v>0</v>
+      </c>
+      <c r="AI279">
+        <v>0</v>
+      </c>
+      <c r="AJ279" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK279" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AL279" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM279">
+        <v>973593</v>
+      </c>
+      <c r="AN279">
+        <v>135464</v>
+      </c>
+      <c r="AS279" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT279" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AU279" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV279" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="280" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>48</v>
+      </c>
+      <c r="B280" t="s">
+        <v>998</v>
+      </c>
+      <c r="C280" t="s">
+        <v>284</v>
+      </c>
+      <c r="D280" t="s">
+        <v>999</v>
+      </c>
+      <c r="E280" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F280" t="s">
+        <v>53</v>
+      </c>
+      <c r="G280" t="s">
+        <v>442</v>
+      </c>
+      <c r="H280" t="s">
+        <v>108</v>
+      </c>
+      <c r="I280">
+        <v>4639</v>
+      </c>
+      <c r="J280" t="s">
+        <v>56</v>
+      </c>
+      <c r="K280">
+        <v>118125</v>
+      </c>
+      <c r="L280">
+        <v>118125</v>
+      </c>
+      <c r="M280">
+        <v>24</v>
+      </c>
+      <c r="N280">
+        <v>16</v>
+      </c>
+      <c r="O280" t="s">
+        <v>907</v>
+      </c>
+      <c r="P280">
+        <v>118125</v>
+      </c>
+      <c r="Q280">
+        <v>118125</v>
+      </c>
+      <c r="R280" t="s">
+        <v>58</v>
+      </c>
+      <c r="S280">
+        <v>12</v>
+      </c>
+      <c r="T280">
+        <v>12</v>
+      </c>
+      <c r="U280">
+        <v>1</v>
+      </c>
+      <c r="V280">
+        <v>10</v>
+      </c>
+      <c r="W280" t="s">
+        <v>90</v>
+      </c>
+      <c r="X280" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y280" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z280" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA280" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB280" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD280" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE280" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF280" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG280">
+        <v>-406</v>
+      </c>
+      <c r="AH280">
+        <v>0</v>
+      </c>
+      <c r="AI280">
+        <v>0</v>
+      </c>
+      <c r="AJ280" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK280" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AL280" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM280">
+        <v>973593</v>
+      </c>
+      <c r="AN280">
+        <v>135464</v>
+      </c>
+      <c r="AS280" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT280" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AU280" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV280" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="281" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>48</v>
+      </c>
+      <c r="B281" t="s">
+        <v>998</v>
+      </c>
+      <c r="C281" t="s">
+        <v>284</v>
+      </c>
+      <c r="D281" t="s">
+        <v>999</v>
+      </c>
+      <c r="E281" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F281" t="s">
+        <v>53</v>
+      </c>
+      <c r="G281" t="s">
+        <v>442</v>
+      </c>
+      <c r="H281" t="s">
+        <v>108</v>
+      </c>
+      <c r="I281">
+        <v>4639</v>
+      </c>
+      <c r="J281" t="s">
+        <v>56</v>
+      </c>
+      <c r="K281">
+        <v>118125</v>
+      </c>
+      <c r="L281">
+        <v>118125</v>
+      </c>
+      <c r="M281">
+        <v>24</v>
+      </c>
+      <c r="N281">
+        <v>16</v>
+      </c>
+      <c r="O281" t="s">
+        <v>907</v>
+      </c>
+      <c r="P281">
+        <v>118125</v>
+      </c>
+      <c r="Q281">
+        <v>118125</v>
+      </c>
+      <c r="R281" t="s">
+        <v>58</v>
+      </c>
+      <c r="S281">
+        <v>12</v>
+      </c>
+      <c r="T281">
+        <v>12</v>
+      </c>
+      <c r="U281">
+        <v>1</v>
+      </c>
+      <c r="V281">
+        <v>11</v>
+      </c>
+      <c r="W281" t="s">
+        <v>90</v>
+      </c>
+      <c r="X281" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y281" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z281" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA281" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB281" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD281" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE281" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF281" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG281">
+        <v>-406</v>
+      </c>
+      <c r="AH281">
+        <v>0</v>
+      </c>
+      <c r="AI281">
+        <v>0</v>
+      </c>
+      <c r="AJ281" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK281" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AL281" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM281">
+        <v>973593</v>
+      </c>
+      <c r="AN281">
+        <v>135464</v>
+      </c>
+      <c r="AS281" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT281" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AU281" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV281" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="282" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>48</v>
+      </c>
+      <c r="B282" t="s">
+        <v>998</v>
+      </c>
+      <c r="C282" t="s">
+        <v>284</v>
+      </c>
+      <c r="D282" t="s">
+        <v>999</v>
+      </c>
+      <c r="E282" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F282" t="s">
+        <v>53</v>
+      </c>
+      <c r="G282" t="s">
+        <v>442</v>
+      </c>
+      <c r="H282" t="s">
+        <v>108</v>
+      </c>
+      <c r="I282">
+        <v>4639</v>
+      </c>
+      <c r="J282" t="s">
+        <v>56</v>
+      </c>
+      <c r="K282">
+        <v>118125</v>
+      </c>
+      <c r="L282">
+        <v>118125</v>
+      </c>
+      <c r="M282">
+        <v>24</v>
+      </c>
+      <c r="N282">
+        <v>16</v>
+      </c>
+      <c r="O282" t="s">
+        <v>907</v>
+      </c>
+      <c r="P282">
+        <v>118125</v>
+      </c>
+      <c r="Q282">
+        <v>118125</v>
+      </c>
+      <c r="R282" t="s">
+        <v>58</v>
+      </c>
+      <c r="S282">
+        <v>12</v>
+      </c>
+      <c r="T282">
+        <v>12</v>
+      </c>
+      <c r="U282">
+        <v>1</v>
+      </c>
+      <c r="V282">
+        <v>12</v>
+      </c>
+      <c r="W282" t="s">
+        <v>90</v>
+      </c>
+      <c r="X282" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y282" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z282" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA282" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB282" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD282" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE282" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF282" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG282">
+        <v>-406</v>
+      </c>
+      <c r="AH282">
+        <v>0</v>
+      </c>
+      <c r="AI282">
+        <v>0</v>
+      </c>
+      <c r="AJ282" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK282" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AL282" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM282">
+        <v>973593</v>
+      </c>
+      <c r="AN282">
+        <v>135464</v>
+      </c>
+      <c r="AS282" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT282" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AU282" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV282" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="283" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>48</v>
+      </c>
+      <c r="B283" t="s">
+        <v>322</v>
+      </c>
+      <c r="C283" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D283" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E283" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F283" t="s">
+        <v>53</v>
+      </c>
+      <c r="G283" t="s">
+        <v>98</v>
+      </c>
+      <c r="H283" t="s">
+        <v>108</v>
+      </c>
+      <c r="I283">
+        <v>4049</v>
+      </c>
+      <c r="J283" t="s">
+        <v>56</v>
+      </c>
+      <c r="K283">
+        <v>59574</v>
+      </c>
+      <c r="L283">
+        <v>59574</v>
+      </c>
+      <c r="M283">
+        <v>47</v>
+      </c>
+      <c r="N283">
+        <v>5</v>
+      </c>
+      <c r="O283" t="s">
+        <v>907</v>
+      </c>
+      <c r="P283">
+        <v>59574</v>
+      </c>
+      <c r="Q283">
+        <v>59574</v>
+      </c>
+      <c r="R283" t="s">
+        <v>58</v>
+      </c>
+      <c r="S283">
+        <v>45</v>
+      </c>
+      <c r="T283">
+        <v>3</v>
+      </c>
+      <c r="U283">
+        <v>1</v>
+      </c>
+      <c r="V283">
+        <v>2</v>
+      </c>
+      <c r="W283" t="s">
+        <v>90</v>
+      </c>
+      <c r="X283" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y283" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z283" t="s">
+        <v>1007</v>
+      </c>
+      <c r="AA283" t="s">
+        <v>1007</v>
+      </c>
+      <c r="AB283" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD283" t="s">
+        <v>634</v>
+      </c>
+      <c r="AE283" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF283" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG283">
+        <v>-30</v>
+      </c>
+      <c r="AH283">
+        <v>0</v>
+      </c>
+      <c r="AI283">
+        <v>0</v>
+      </c>
+      <c r="AJ283" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK283" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL283" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM283">
+        <v>973595</v>
+      </c>
+      <c r="AN283">
+        <v>135215</v>
+      </c>
+      <c r="AS283" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT283" t="s">
+        <v>1008</v>
+      </c>
+      <c r="AU283" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV283" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="284" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>48</v>
+      </c>
+      <c r="B284" t="s">
+        <v>322</v>
+      </c>
+      <c r="C284" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D284" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E284" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F284" t="s">
+        <v>53</v>
+      </c>
+      <c r="G284" t="s">
+        <v>98</v>
+      </c>
+      <c r="H284" t="s">
+        <v>108</v>
+      </c>
+      <c r="I284">
+        <v>4049</v>
+      </c>
+      <c r="J284" t="s">
+        <v>56</v>
+      </c>
+      <c r="K284">
+        <v>59574</v>
+      </c>
+      <c r="L284">
+        <v>59574</v>
+      </c>
+      <c r="M284">
+        <v>47</v>
+      </c>
+      <c r="N284">
+        <v>5</v>
+      </c>
+      <c r="O284" t="s">
+        <v>907</v>
+      </c>
+      <c r="P284">
+        <v>426</v>
+      </c>
+      <c r="Q284">
+        <v>426</v>
+      </c>
+      <c r="R284" t="s">
+        <v>58</v>
+      </c>
+      <c r="S284">
+        <v>45</v>
+      </c>
+      <c r="T284">
+        <v>3</v>
+      </c>
+      <c r="U284">
+        <v>1</v>
+      </c>
+      <c r="V284">
+        <v>3</v>
+      </c>
+      <c r="W284" t="s">
+        <v>90</v>
+      </c>
+      <c r="X284" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y284" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z284" t="s">
+        <v>1007</v>
+      </c>
+      <c r="AA284" t="s">
+        <v>1007</v>
+      </c>
+      <c r="AB284" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD284" t="s">
+        <v>634</v>
+      </c>
+      <c r="AE284" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF284" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG284">
+        <v>-30</v>
+      </c>
+      <c r="AH284">
+        <v>0</v>
+      </c>
+      <c r="AI284">
+        <v>0</v>
+      </c>
+      <c r="AJ284" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK284" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL284" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM284">
+        <v>973595</v>
+      </c>
+      <c r="AN284">
+        <v>135215</v>
+      </c>
+      <c r="AS284" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT284" t="s">
+        <v>1008</v>
+      </c>
+      <c r="AU284" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV284" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="285" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>48</v>
+      </c>
+      <c r="B285" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C285" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D285" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E285" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F285" t="s">
+        <v>53</v>
+      </c>
+      <c r="G285" t="s">
+        <v>274</v>
+      </c>
+      <c r="H285" t="s">
+        <v>108</v>
+      </c>
+      <c r="I285">
+        <v>2802</v>
+      </c>
+      <c r="J285" t="s">
+        <v>56</v>
+      </c>
+      <c r="K285">
+        <v>40000</v>
+      </c>
+      <c r="L285">
+        <v>40000</v>
+      </c>
+      <c r="M285">
+        <v>60</v>
+      </c>
+      <c r="N285">
+        <v>10</v>
+      </c>
+      <c r="O285" t="s">
+        <v>907</v>
+      </c>
+      <c r="P285">
+        <v>40000</v>
+      </c>
+      <c r="Q285">
+        <v>40000</v>
+      </c>
+      <c r="R285" t="s">
+        <v>58</v>
+      </c>
+      <c r="S285">
+        <v>54</v>
+      </c>
+      <c r="T285">
+        <v>6</v>
+      </c>
+      <c r="U285">
+        <v>1</v>
+      </c>
+      <c r="V285">
+        <v>6</v>
+      </c>
+      <c r="W285" t="s">
+        <v>90</v>
+      </c>
+      <c r="X285" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y285" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z285" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA285" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB285" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD285" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE285" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF285" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG285">
+        <v>-35</v>
+      </c>
+      <c r="AH285">
+        <v>0</v>
+      </c>
+      <c r="AI285">
+        <v>0</v>
+      </c>
+      <c r="AJ285" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK285" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL285" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM285">
+        <v>973596</v>
+      </c>
+      <c r="AN285">
+        <v>134876</v>
+      </c>
+      <c r="AS285" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT285" t="s">
+        <v>1014</v>
+      </c>
+      <c r="AU285" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV285" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="286" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>48</v>
+      </c>
+      <c r="B286" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C286" t="s">
+        <v>259</v>
+      </c>
+      <c r="D286" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E286" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F286" t="s">
+        <v>53</v>
+      </c>
+      <c r="G286" t="s">
+        <v>88</v>
+      </c>
+      <c r="H286" t="s">
+        <v>89</v>
+      </c>
+      <c r="I286">
+        <v>408</v>
+      </c>
+      <c r="J286" t="s">
+        <v>56</v>
+      </c>
+      <c r="K286">
+        <v>58333</v>
+      </c>
+      <c r="L286">
+        <v>58333</v>
+      </c>
+      <c r="M286">
+        <v>24</v>
+      </c>
+      <c r="N286">
+        <v>30</v>
+      </c>
+      <c r="O286" t="s">
+        <v>718</v>
+      </c>
+      <c r="P286">
+        <v>58333</v>
+      </c>
+      <c r="Q286">
+        <v>58333</v>
+      </c>
+      <c r="R286" t="s">
+        <v>58</v>
+      </c>
+      <c r="S286">
+        <v>7</v>
+      </c>
+      <c r="T286">
+        <v>17</v>
+      </c>
+      <c r="U286">
+        <v>1</v>
+      </c>
+      <c r="V286">
+        <v>17</v>
+      </c>
+      <c r="W286" t="s">
+        <v>90</v>
+      </c>
+      <c r="X286" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y286" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z286" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA286" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB286" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC286" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD286" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE286" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF286" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG286">
+        <v>-25</v>
+      </c>
+      <c r="AH286">
+        <v>1</v>
+      </c>
+      <c r="AI286">
+        <v>0</v>
+      </c>
+      <c r="AJ286" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK286" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL286" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM286">
+        <v>973598</v>
+      </c>
+      <c r="AN286">
+        <v>133383</v>
+      </c>
+      <c r="AS286" t="s">
+        <v>177</v>
+      </c>
+      <c r="AT286" t="s">
+        <v>1019</v>
+      </c>
+      <c r="AV286" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="287" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>48</v>
+      </c>
+      <c r="B287" t="s">
+        <v>502</v>
+      </c>
+      <c r="C287" t="s">
+        <v>689</v>
+      </c>
+      <c r="D287" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E287" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F287" t="s">
+        <v>53</v>
+      </c>
+      <c r="G287" t="s">
+        <v>612</v>
+      </c>
+      <c r="H287" t="s">
+        <v>108</v>
+      </c>
+      <c r="I287">
+        <v>1059</v>
+      </c>
+      <c r="J287" t="s">
+        <v>56</v>
+      </c>
+      <c r="K287">
+        <v>40000</v>
+      </c>
+      <c r="L287">
+        <v>40000</v>
+      </c>
+      <c r="M287">
+        <v>34</v>
+      </c>
+      <c r="N287">
+        <v>5</v>
+      </c>
+      <c r="O287" t="s">
+        <v>907</v>
+      </c>
+      <c r="P287">
+        <v>40000</v>
+      </c>
+      <c r="Q287">
+        <v>40000</v>
+      </c>
+      <c r="R287" t="s">
+        <v>58</v>
+      </c>
+      <c r="S287">
+        <v>28</v>
+      </c>
+      <c r="T287">
+        <v>6</v>
+      </c>
+      <c r="U287">
+        <v>1</v>
+      </c>
+      <c r="V287">
+        <v>6</v>
+      </c>
+      <c r="W287" t="s">
+        <v>90</v>
+      </c>
+      <c r="X287" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y287" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z287" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA287" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB287" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC287" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD287" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE287" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF287" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG287">
+        <v>0</v>
+      </c>
+      <c r="AH287">
+        <v>0</v>
+      </c>
+      <c r="AI287">
+        <v>0</v>
+      </c>
+      <c r="AJ287" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK287" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL287" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM287">
+        <v>973599</v>
+      </c>
+      <c r="AN287">
+        <v>134162</v>
+      </c>
+      <c r="AS287" t="s">
+        <v>140</v>
+      </c>
+      <c r="AT287" t="s">
+        <v>1023</v>
+      </c>
+      <c r="AU287" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV287" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="288" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>48</v>
+      </c>
+      <c r="B288" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C288" t="s">
+        <v>887</v>
+      </c>
+      <c r="D288" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E288" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F288" t="s">
+        <v>53</v>
+      </c>
+      <c r="G288" t="s">
+        <v>349</v>
+      </c>
+      <c r="H288" t="s">
+        <v>108</v>
+      </c>
+      <c r="I288">
+        <v>2415</v>
+      </c>
+      <c r="J288" t="s">
+        <v>56</v>
+      </c>
+      <c r="K288">
+        <v>42500</v>
+      </c>
+      <c r="L288">
+        <v>42500</v>
+      </c>
+      <c r="M288">
+        <v>36</v>
+      </c>
+      <c r="N288">
+        <v>1</v>
+      </c>
+      <c r="O288" t="s">
+        <v>907</v>
+      </c>
+      <c r="P288">
+        <v>42500</v>
+      </c>
+      <c r="Q288">
+        <v>42500</v>
+      </c>
+      <c r="R288" t="s">
+        <v>58</v>
+      </c>
+      <c r="S288">
+        <v>26</v>
+      </c>
+      <c r="T288">
+        <v>10</v>
+      </c>
+      <c r="U288">
+        <v>1</v>
+      </c>
+      <c r="V288">
+        <v>8</v>
+      </c>
+      <c r="W288" t="s">
+        <v>90</v>
+      </c>
+      <c r="X288" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y288" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z288" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA288" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB288" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD288" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE288" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF288" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG288">
+        <v>-149</v>
+      </c>
+      <c r="AH288">
+        <v>0</v>
+      </c>
+      <c r="AI288">
+        <v>0</v>
+      </c>
+      <c r="AJ288" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK288" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL288" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM288">
+        <v>973601</v>
+      </c>
+      <c r="AN288">
+        <v>134756</v>
+      </c>
+      <c r="AS288" t="s">
+        <v>177</v>
+      </c>
+      <c r="AT288" t="s">
+        <v>1028</v>
+      </c>
+      <c r="AU288" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV288" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="289" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>48</v>
+      </c>
+      <c r="B289" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C289" t="s">
+        <v>887</v>
+      </c>
+      <c r="D289" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E289" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F289" t="s">
+        <v>53</v>
+      </c>
+      <c r="G289" t="s">
+        <v>349</v>
+      </c>
+      <c r="H289" t="s">
+        <v>108</v>
+      </c>
+      <c r="I289">
+        <v>2415</v>
+      </c>
+      <c r="J289" t="s">
+        <v>56</v>
+      </c>
+      <c r="K289">
+        <v>42500</v>
+      </c>
+      <c r="L289">
+        <v>42500</v>
+      </c>
+      <c r="M289">
+        <v>36</v>
+      </c>
+      <c r="N289">
+        <v>1</v>
+      </c>
+      <c r="O289" t="s">
+        <v>907</v>
+      </c>
+      <c r="P289">
+        <v>42500</v>
+      </c>
+      <c r="Q289">
+        <v>42500</v>
+      </c>
+      <c r="R289" t="s">
+        <v>58</v>
+      </c>
+      <c r="S289">
+        <v>26</v>
+      </c>
+      <c r="T289">
+        <v>10</v>
+      </c>
+      <c r="U289">
+        <v>1</v>
+      </c>
+      <c r="V289">
+        <v>9</v>
+      </c>
+      <c r="W289" t="s">
+        <v>90</v>
+      </c>
+      <c r="X289" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y289" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z289" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA289" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB289" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD289" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE289" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF289" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG289">
+        <v>-149</v>
+      </c>
+      <c r="AH289">
+        <v>0</v>
+      </c>
+      <c r="AI289">
+        <v>0</v>
+      </c>
+      <c r="AJ289" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK289" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL289" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM289">
+        <v>973601</v>
+      </c>
+      <c r="AN289">
+        <v>134756</v>
+      </c>
+      <c r="AS289" t="s">
+        <v>177</v>
+      </c>
+      <c r="AT289" t="s">
+        <v>1028</v>
+      </c>
+      <c r="AU289" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV289" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="290" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>48</v>
+      </c>
+      <c r="B290" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C290" t="s">
+        <v>887</v>
+      </c>
+      <c r="D290" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E290" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F290" t="s">
+        <v>53</v>
+      </c>
+      <c r="G290" t="s">
+        <v>349</v>
+      </c>
+      <c r="H290" t="s">
+        <v>108</v>
+      </c>
+      <c r="I290">
+        <v>2415</v>
+      </c>
+      <c r="J290" t="s">
+        <v>56</v>
+      </c>
+      <c r="K290">
+        <v>42500</v>
+      </c>
+      <c r="L290">
+        <v>42500</v>
+      </c>
+      <c r="M290">
+        <v>36</v>
+      </c>
+      <c r="N290">
+        <v>1</v>
+      </c>
+      <c r="O290" t="s">
+        <v>907</v>
+      </c>
+      <c r="P290">
+        <v>42500</v>
+      </c>
+      <c r="Q290">
+        <v>42500</v>
+      </c>
+      <c r="R290" t="s">
+        <v>58</v>
+      </c>
+      <c r="S290">
+        <v>26</v>
+      </c>
+      <c r="T290">
+        <v>10</v>
+      </c>
+      <c r="U290">
+        <v>1</v>
+      </c>
+      <c r="V290">
+        <v>10</v>
+      </c>
+      <c r="W290" t="s">
+        <v>90</v>
+      </c>
+      <c r="X290" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y290" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z290" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA290" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB290" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD290" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE290" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF290" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG290">
+        <v>-149</v>
+      </c>
+      <c r="AH290">
+        <v>0</v>
+      </c>
+      <c r="AI290">
+        <v>0</v>
+      </c>
+      <c r="AJ290" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK290" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL290" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM290">
+        <v>973601</v>
+      </c>
+      <c r="AN290">
+        <v>134756</v>
+      </c>
+      <c r="AS290" t="s">
+        <v>177</v>
+      </c>
+      <c r="AT290" t="s">
+        <v>1028</v>
+      </c>
+      <c r="AU290" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV290" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="291" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>48</v>
+      </c>
+      <c r="B291" t="s">
+        <v>49</v>
+      </c>
+      <c r="C291" t="s">
+        <v>785</v>
+      </c>
+      <c r="D291" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E291" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F291" t="s">
+        <v>53</v>
+      </c>
+      <c r="G291" t="s">
+        <v>75</v>
+      </c>
+      <c r="H291" t="s">
+        <v>55</v>
+      </c>
+      <c r="I291">
+        <v>3071</v>
+      </c>
+      <c r="J291" t="s">
+        <v>56</v>
+      </c>
+      <c r="K291">
+        <v>49500</v>
+      </c>
+      <c r="L291">
+        <v>49500</v>
+      </c>
+      <c r="M291">
+        <v>21</v>
+      </c>
+      <c r="N291">
+        <v>8</v>
+      </c>
+      <c r="O291" t="s">
+        <v>907</v>
+      </c>
+      <c r="P291">
+        <v>49500</v>
+      </c>
+      <c r="Q291">
+        <v>49500</v>
+      </c>
+      <c r="R291" t="s">
+        <v>58</v>
+      </c>
+      <c r="S291">
+        <v>15</v>
+      </c>
+      <c r="T291">
+        <v>6</v>
+      </c>
+      <c r="U291">
+        <v>1</v>
+      </c>
+      <c r="V291">
+        <v>6</v>
+      </c>
+      <c r="W291" t="s">
+        <v>7</v>
+      </c>
+      <c r="X291" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y291" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z291" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA291" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB291" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC291" t="s">
+        <v>810</v>
+      </c>
+      <c r="AD291" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE291" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF291" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG291">
+        <v>-33</v>
+      </c>
+      <c r="AH291">
+        <v>0</v>
+      </c>
+      <c r="AI291">
+        <v>0</v>
+      </c>
+      <c r="AJ291" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK291" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL291" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM291">
+        <v>973602</v>
+      </c>
+      <c r="AN291">
+        <v>134962</v>
+      </c>
+      <c r="AS291" t="s">
+        <v>582</v>
+      </c>
+      <c r="AT291" t="s">
+        <v>293</v>
+      </c>
+      <c r="AU291" t="s">
+        <v>1032</v>
+      </c>
+      <c r="AV291" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="292" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>48</v>
+      </c>
+      <c r="B292" t="s">
+        <v>156</v>
+      </c>
+      <c r="C292" t="s">
+        <v>419</v>
+      </c>
+      <c r="D292" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E292" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F292" t="s">
+        <v>53</v>
+      </c>
+      <c r="G292" t="s">
+        <v>234</v>
+      </c>
+      <c r="H292" t="s">
+        <v>89</v>
+      </c>
+      <c r="I292">
+        <v>956</v>
+      </c>
+      <c r="J292" t="s">
+        <v>56</v>
+      </c>
+      <c r="K292">
+        <v>53333</v>
+      </c>
+      <c r="L292">
+        <v>53333</v>
+      </c>
+      <c r="M292">
+        <v>36</v>
+      </c>
+      <c r="N292">
+        <v>5</v>
+      </c>
+      <c r="O292" t="s">
+        <v>907</v>
+      </c>
+      <c r="P292">
+        <v>53166</v>
+      </c>
+      <c r="Q292">
+        <v>53166</v>
+      </c>
+      <c r="R292" t="s">
+        <v>58</v>
+      </c>
+      <c r="S292">
+        <v>21</v>
+      </c>
+      <c r="T292">
+        <v>15</v>
+      </c>
+      <c r="U292">
+        <v>1</v>
+      </c>
+      <c r="V292">
+        <v>15</v>
+      </c>
+      <c r="W292" t="s">
+        <v>7</v>
+      </c>
+      <c r="X292" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y292" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z292" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AA292" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AB292" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC292" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD292" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AE292" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF292" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG292">
+        <v>-30</v>
+      </c>
+      <c r="AH292">
+        <v>23</v>
+      </c>
+      <c r="AI292">
+        <v>0</v>
+      </c>
+      <c r="AJ292" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK292" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL292" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM292">
+        <v>973604</v>
+      </c>
+      <c r="AN292">
+        <v>133481</v>
+      </c>
+      <c r="AS292" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT292" t="s">
+        <v>1038</v>
+      </c>
+      <c r="AV292" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="293" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>48</v>
+      </c>
+      <c r="B293" t="s">
+        <v>156</v>
+      </c>
+      <c r="C293" t="s">
+        <v>419</v>
+      </c>
+      <c r="D293" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E293" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F293" t="s">
+        <v>53</v>
+      </c>
+      <c r="G293" t="s">
+        <v>234</v>
+      </c>
+      <c r="H293" t="s">
+        <v>89</v>
+      </c>
+      <c r="I293">
+        <v>955</v>
+      </c>
+      <c r="J293" t="s">
+        <v>56</v>
+      </c>
+      <c r="K293">
+        <v>53333</v>
+      </c>
+      <c r="L293">
+        <v>53333</v>
+      </c>
+      <c r="M293">
+        <v>36</v>
+      </c>
+      <c r="N293">
+        <v>5</v>
+      </c>
+      <c r="O293" t="s">
+        <v>907</v>
+      </c>
+      <c r="P293">
+        <v>53166</v>
+      </c>
+      <c r="Q293">
+        <v>53166</v>
+      </c>
+      <c r="R293" t="s">
+        <v>58</v>
+      </c>
+      <c r="S293">
+        <v>21</v>
+      </c>
+      <c r="T293">
+        <v>15</v>
+      </c>
+      <c r="U293">
+        <v>1</v>
+      </c>
+      <c r="V293">
+        <v>15</v>
+      </c>
+      <c r="W293" t="s">
+        <v>90</v>
+      </c>
+      <c r="X293" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y293" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z293" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AA293" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AB293" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC293" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD293" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AE293" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF293" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG293">
+        <v>-30</v>
+      </c>
+      <c r="AH293">
+        <v>23</v>
+      </c>
+      <c r="AI293">
+        <v>0</v>
+      </c>
+      <c r="AJ293" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK293" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL293" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM293">
+        <v>973606</v>
+      </c>
+      <c r="AN293">
+        <v>133482</v>
+      </c>
+      <c r="AS293" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT293" t="s">
+        <v>1042</v>
+      </c>
+      <c r="AV293" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="294" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>48</v>
+      </c>
+      <c r="B294" t="s">
+        <v>322</v>
+      </c>
+      <c r="C294" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D294" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E294" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F294" t="s">
+        <v>53</v>
+      </c>
+      <c r="G294" t="s">
+        <v>147</v>
+      </c>
+      <c r="H294" t="s">
+        <v>108</v>
+      </c>
+      <c r="I294">
+        <v>4468</v>
+      </c>
+      <c r="J294" t="s">
+        <v>56</v>
+      </c>
+      <c r="K294">
+        <v>39167</v>
+      </c>
+      <c r="L294">
+        <v>39167</v>
+      </c>
+      <c r="M294">
+        <v>60</v>
+      </c>
+      <c r="N294">
+        <v>5</v>
+      </c>
+      <c r="O294" t="s">
+        <v>907</v>
+      </c>
+      <c r="P294">
+        <v>39167</v>
+      </c>
+      <c r="Q294">
+        <v>39167</v>
+      </c>
+      <c r="R294" t="s">
+        <v>58</v>
+      </c>
+      <c r="S294">
+        <v>59</v>
+      </c>
+      <c r="T294">
+        <v>2</v>
+      </c>
+      <c r="U294">
+        <v>1</v>
+      </c>
+      <c r="V294">
+        <v>1</v>
+      </c>
+      <c r="W294" t="s">
+        <v>7</v>
+      </c>
+      <c r="X294" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y294" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z294" t="s">
+        <v>913</v>
+      </c>
+      <c r="AA294" t="s">
+        <v>913</v>
+      </c>
+      <c r="AB294" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD294" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE294" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF294" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG294">
+        <v>-30</v>
+      </c>
+      <c r="AH294">
+        <v>0</v>
+      </c>
+      <c r="AI294">
+        <v>0</v>
+      </c>
+      <c r="AJ294" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK294" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL294" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM294">
+        <v>973608</v>
+      </c>
+      <c r="AN294">
+        <v>135370</v>
+      </c>
+      <c r="AS294" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT294" t="s">
+        <v>1047</v>
+      </c>
+      <c r="AU294" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV294" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="295" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>48</v>
+      </c>
+      <c r="B295" t="s">
+        <v>322</v>
+      </c>
+      <c r="C295" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D295" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E295" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F295" t="s">
+        <v>53</v>
+      </c>
+      <c r="G295" t="s">
+        <v>147</v>
+      </c>
+      <c r="H295" t="s">
+        <v>108</v>
+      </c>
+      <c r="I295">
+        <v>4468</v>
+      </c>
+      <c r="J295" t="s">
+        <v>56</v>
+      </c>
+      <c r="K295">
+        <v>39167</v>
+      </c>
+      <c r="L295">
+        <v>39167</v>
+      </c>
+      <c r="M295">
+        <v>60</v>
+      </c>
+      <c r="N295">
+        <v>5</v>
+      </c>
+      <c r="O295" t="s">
+        <v>907</v>
+      </c>
+      <c r="P295">
+        <v>833</v>
+      </c>
+      <c r="Q295">
+        <v>833</v>
+      </c>
+      <c r="R295" t="s">
+        <v>58</v>
+      </c>
+      <c r="S295">
+        <v>59</v>
+      </c>
+      <c r="T295">
+        <v>2</v>
+      </c>
+      <c r="U295">
+        <v>1</v>
+      </c>
+      <c r="V295">
+        <v>2</v>
+      </c>
+      <c r="W295" t="s">
+        <v>7</v>
+      </c>
+      <c r="X295" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y295" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z295" t="s">
+        <v>913</v>
+      </c>
+      <c r="AA295" t="s">
+        <v>913</v>
+      </c>
+      <c r="AB295" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD295" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE295" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF295" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG295">
+        <v>-30</v>
+      </c>
+      <c r="AH295">
+        <v>0</v>
+      </c>
+      <c r="AI295">
+        <v>0</v>
+      </c>
+      <c r="AJ295" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK295" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL295" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM295">
+        <v>973608</v>
+      </c>
+      <c r="AN295">
+        <v>135370</v>
+      </c>
+      <c r="AS295" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT295" t="s">
+        <v>1047</v>
+      </c>
+      <c r="AU295" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV295" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="296" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>48</v>
+      </c>
+      <c r="B296" t="s">
+        <v>114</v>
+      </c>
+      <c r="C296" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D296" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E296" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F296" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G296" t="s">
+        <v>1053</v>
+      </c>
+      <c r="H296" t="s">
+        <v>108</v>
+      </c>
+      <c r="I296">
+        <v>1612</v>
+      </c>
+      <c r="J296" t="s">
+        <v>56</v>
+      </c>
+      <c r="K296">
+        <v>75000</v>
+      </c>
+      <c r="L296">
+        <v>75000</v>
+      </c>
+      <c r="M296">
+        <v>24</v>
+      </c>
+      <c r="N296">
+        <v>5</v>
+      </c>
+      <c r="O296" t="s">
+        <v>907</v>
+      </c>
+      <c r="P296">
+        <v>75000</v>
+      </c>
+      <c r="Q296">
+        <v>75000</v>
+      </c>
+      <c r="R296" t="s">
+        <v>58</v>
+      </c>
+      <c r="S296">
+        <v>14</v>
+      </c>
+      <c r="T296">
+        <v>10</v>
+      </c>
+      <c r="U296">
+        <v>1</v>
+      </c>
+      <c r="V296">
+        <v>10</v>
+      </c>
+      <c r="W296" t="s">
+        <v>90</v>
+      </c>
+      <c r="X296" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y296" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z296" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA296" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB296" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC296" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD296" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE296" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF296" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG296">
+        <v>-30</v>
+      </c>
+      <c r="AH296">
+        <v>0</v>
+      </c>
+      <c r="AI296">
+        <v>0</v>
+      </c>
+      <c r="AJ296" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK296" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL296" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM296">
+        <v>973610</v>
+      </c>
+      <c r="AN296">
+        <v>134446</v>
+      </c>
+      <c r="AS296" t="s">
+        <v>191</v>
+      </c>
+      <c r="AT296" t="s">
+        <v>1054</v>
+      </c>
+      <c r="AV296" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="297" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>48</v>
+      </c>
+      <c r="B297" t="s">
+        <v>296</v>
+      </c>
+      <c r="C297" t="s">
+        <v>533</v>
+      </c>
+      <c r="D297" t="s">
+        <v>534</v>
+      </c>
+      <c r="E297" t="s">
+        <v>535</v>
+      </c>
+      <c r="F297" t="s">
+        <v>53</v>
+      </c>
+      <c r="G297" t="s">
+        <v>190</v>
+      </c>
+      <c r="H297" t="s">
+        <v>108</v>
+      </c>
+      <c r="I297">
+        <v>2899</v>
+      </c>
+      <c r="J297" t="s">
+        <v>56</v>
+      </c>
+      <c r="K297">
+        <v>192917</v>
+      </c>
+      <c r="L297">
+        <v>192917</v>
+      </c>
+      <c r="M297">
+        <v>12</v>
+      </c>
+      <c r="N297">
+        <v>10</v>
+      </c>
+      <c r="O297" t="s">
+        <v>907</v>
+      </c>
+      <c r="P297">
+        <v>192917</v>
+      </c>
+      <c r="Q297">
+        <v>192917</v>
+      </c>
+      <c r="R297" t="s">
+        <v>58</v>
+      </c>
+      <c r="S297">
+        <v>2</v>
+      </c>
+      <c r="T297">
+        <v>10</v>
+      </c>
+      <c r="U297">
+        <v>1</v>
+      </c>
+      <c r="V297">
+        <v>10</v>
+      </c>
+      <c r="W297" t="s">
+        <v>90</v>
+      </c>
+      <c r="X297" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y297" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z297" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA297" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB297" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD297" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE297" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF297" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG297">
+        <v>-158</v>
+      </c>
+      <c r="AH297">
+        <v>0</v>
+      </c>
+      <c r="AI297">
+        <v>0</v>
+      </c>
+      <c r="AJ297" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK297" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL297" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM297">
+        <v>973612</v>
+      </c>
+      <c r="AN297">
+        <v>134899</v>
+      </c>
+      <c r="AS297" t="s">
+        <v>152</v>
+      </c>
+      <c r="AT297" t="s">
+        <v>536</v>
+      </c>
+      <c r="AV297" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="298" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>48</v>
+      </c>
+      <c r="B298" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C298" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D298" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E298" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F298" t="s">
+        <v>53</v>
+      </c>
+      <c r="G298" t="s">
+        <v>612</v>
+      </c>
+      <c r="H298" t="s">
+        <v>89</v>
+      </c>
+      <c r="I298">
+        <v>149</v>
+      </c>
+      <c r="J298" t="s">
+        <v>56</v>
+      </c>
+      <c r="K298">
+        <v>28000</v>
+      </c>
+      <c r="L298">
+        <v>28000</v>
+      </c>
+      <c r="M298">
+        <v>36</v>
+      </c>
+      <c r="N298">
+        <v>5</v>
+      </c>
+      <c r="O298" t="s">
+        <v>907</v>
+      </c>
+      <c r="P298">
+        <v>28000</v>
+      </c>
+      <c r="Q298">
+        <v>28000</v>
+      </c>
+      <c r="R298" t="s">
+        <v>58</v>
+      </c>
+      <c r="S298">
+        <v>17</v>
+      </c>
+      <c r="T298">
+        <v>19</v>
+      </c>
+      <c r="U298">
+        <v>1</v>
+      </c>
+      <c r="V298">
+        <v>19</v>
+      </c>
+      <c r="W298" t="s">
+        <v>7</v>
+      </c>
+      <c r="X298" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y298" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z298" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA298" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB298" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC298" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD298" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE298" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF298" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG298">
+        <v>-30</v>
+      </c>
+      <c r="AH298">
+        <v>0</v>
+      </c>
+      <c r="AI298">
+        <v>0</v>
+      </c>
+      <c r="AJ298" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK298" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL298" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM298">
+        <v>973614</v>
+      </c>
+      <c r="AN298">
+        <v>133305</v>
+      </c>
+      <c r="AS298" t="s">
+        <v>177</v>
+      </c>
+      <c r="AT298" t="s">
+        <v>1060</v>
+      </c>
+      <c r="AU298" t="s">
+        <v>1061</v>
+      </c>
+      <c r="AV298" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="299" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>48</v>
+      </c>
+      <c r="B299" t="s">
+        <v>163</v>
+      </c>
+      <c r="C299" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D299" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E299" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F299" t="s">
+        <v>53</v>
+      </c>
+      <c r="G299" t="s">
+        <v>147</v>
+      </c>
+      <c r="H299" t="s">
+        <v>108</v>
+      </c>
+      <c r="I299">
+        <v>1119</v>
+      </c>
+      <c r="J299" t="s">
+        <v>56</v>
+      </c>
+      <c r="K299">
+        <v>35556</v>
+      </c>
+      <c r="L299">
+        <v>35556</v>
+      </c>
+      <c r="M299">
+        <v>36</v>
+      </c>
+      <c r="N299">
+        <v>5</v>
+      </c>
+      <c r="O299" t="s">
+        <v>907</v>
+      </c>
+      <c r="P299">
+        <v>35556</v>
+      </c>
+      <c r="Q299">
+        <v>35556</v>
+      </c>
+      <c r="R299" t="s">
+        <v>58</v>
+      </c>
+      <c r="S299">
+        <v>22</v>
+      </c>
+      <c r="T299">
+        <v>14</v>
+      </c>
+      <c r="U299">
+        <v>1</v>
+      </c>
+      <c r="V299">
+        <v>14</v>
+      </c>
+      <c r="W299" t="s">
+        <v>90</v>
+      </c>
+      <c r="X299" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y299" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z299" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA299" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB299" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC299" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD299" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE299" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF299" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG299">
+        <v>-30</v>
+      </c>
+      <c r="AH299">
+        <v>0</v>
+      </c>
+      <c r="AI299">
+        <v>0</v>
+      </c>
+      <c r="AJ299" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK299" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL299" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM299">
+        <v>973615</v>
+      </c>
+      <c r="AN299">
+        <v>134184</v>
+      </c>
+      <c r="AS299" t="s">
+        <v>140</v>
+      </c>
+      <c r="AT299" t="s">
+        <v>1065</v>
+      </c>
+      <c r="AV299" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="300" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>48</v>
+      </c>
+      <c r="B300" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C300" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D300" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E300" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F300" t="s">
+        <v>53</v>
+      </c>
+      <c r="G300" t="s">
+        <v>612</v>
+      </c>
+      <c r="H300" t="s">
+        <v>89</v>
+      </c>
+      <c r="I300">
+        <v>147</v>
+      </c>
+      <c r="J300" t="s">
+        <v>56</v>
+      </c>
+      <c r="K300">
+        <v>36000</v>
+      </c>
+      <c r="L300">
+        <v>36000</v>
+      </c>
+      <c r="M300">
+        <v>36</v>
+      </c>
+      <c r="N300">
+        <v>5</v>
+      </c>
+      <c r="O300" t="s">
+        <v>907</v>
+      </c>
+      <c r="P300">
+        <v>36000</v>
+      </c>
+      <c r="Q300">
+        <v>36000</v>
+      </c>
+      <c r="R300" t="s">
+        <v>58</v>
+      </c>
+      <c r="S300">
+        <v>17</v>
+      </c>
+      <c r="T300">
+        <v>19</v>
+      </c>
+      <c r="U300">
+        <v>1</v>
+      </c>
+      <c r="V300">
+        <v>19</v>
+      </c>
+      <c r="W300" t="s">
+        <v>7</v>
+      </c>
+      <c r="X300" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y300" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z300" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA300" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB300" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC300" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD300" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE300" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF300" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG300">
+        <v>-30</v>
+      </c>
+      <c r="AH300">
+        <v>0</v>
+      </c>
+      <c r="AI300">
+        <v>0</v>
+      </c>
+      <c r="AJ300" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK300" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL300" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM300">
+        <v>973617</v>
+      </c>
+      <c r="AN300">
+        <v>133288</v>
+      </c>
+      <c r="AS300" t="s">
+        <v>191</v>
+      </c>
+      <c r="AT300" t="s">
+        <v>1069</v>
+      </c>
+      <c r="AU300" t="s">
+        <v>1070</v>
+      </c>
+      <c r="AV300" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="301" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>48</v>
+      </c>
+      <c r="B301" t="s">
+        <v>202</v>
+      </c>
+      <c r="C301" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D301" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E301" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F301" t="s">
+        <v>53</v>
+      </c>
+      <c r="G301" t="s">
+        <v>107</v>
+      </c>
+      <c r="H301" t="s">
+        <v>108</v>
+      </c>
+      <c r="I301">
+        <v>1554</v>
+      </c>
+      <c r="J301" t="s">
+        <v>56</v>
+      </c>
+      <c r="K301">
+        <v>120000</v>
+      </c>
+      <c r="L301">
+        <v>120000</v>
+      </c>
+      <c r="M301">
+        <v>10</v>
+      </c>
+      <c r="N301">
+        <v>5</v>
+      </c>
+      <c r="O301" t="s">
+        <v>907</v>
+      </c>
+      <c r="P301">
+        <v>120000</v>
+      </c>
+      <c r="Q301">
+        <v>120000</v>
+      </c>
+      <c r="R301" t="s">
+        <v>58</v>
+      </c>
+      <c r="S301">
+        <v>0</v>
+      </c>
+      <c r="T301">
+        <v>10</v>
+      </c>
+      <c r="U301">
+        <v>1</v>
+      </c>
+      <c r="V301">
+        <v>10</v>
+      </c>
+      <c r="W301" t="s">
+        <v>90</v>
+      </c>
+      <c r="X301" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y301" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z301" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA301" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB301" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC301" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD301" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE301" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF301" t="s">
+        <v>530</v>
+      </c>
+      <c r="AH301">
+        <v>0</v>
+      </c>
+      <c r="AI301">
+        <v>0</v>
+      </c>
+      <c r="AJ301" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK301" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL301" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM301">
+        <v>973620</v>
+      </c>
+      <c r="AN301">
+        <v>134419</v>
+      </c>
+      <c r="AS301" t="s">
+        <v>140</v>
+      </c>
+      <c r="AT301" t="s">
+        <v>1074</v>
+      </c>
+      <c r="AU301" t="s">
+        <v>1075</v>
+      </c>
+      <c r="AV301" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="302" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>48</v>
+      </c>
+      <c r="B302" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C302" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D302" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E302" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F302" t="s">
+        <v>53</v>
+      </c>
+      <c r="G302" t="s">
+        <v>147</v>
+      </c>
+      <c r="H302" t="s">
+        <v>108</v>
+      </c>
+      <c r="I302">
+        <v>3572</v>
+      </c>
+      <c r="J302" t="s">
+        <v>56</v>
+      </c>
+      <c r="K302">
+        <v>48094</v>
+      </c>
+      <c r="L302">
+        <v>48094</v>
+      </c>
+      <c r="M302">
+        <v>48</v>
+      </c>
+      <c r="N302">
+        <v>4</v>
+      </c>
+      <c r="O302" t="s">
+        <v>907</v>
+      </c>
+      <c r="P302">
+        <v>48094</v>
+      </c>
+      <c r="Q302">
+        <v>48094</v>
+      </c>
+      <c r="R302" t="s">
+        <v>58</v>
+      </c>
+      <c r="S302">
+        <v>45</v>
+      </c>
+      <c r="T302">
+        <v>3</v>
+      </c>
+      <c r="U302">
+        <v>1</v>
+      </c>
+      <c r="V302">
+        <v>3</v>
+      </c>
+      <c r="W302" t="s">
+        <v>90</v>
+      </c>
+      <c r="X302" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y302" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z302" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA302" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB302" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD302" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE302" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF302" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG302">
+        <v>-29</v>
+      </c>
+      <c r="AH302">
+        <v>0</v>
+      </c>
+      <c r="AI302">
+        <v>0</v>
+      </c>
+      <c r="AJ302" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK302" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL302" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM302">
+        <v>973621</v>
+      </c>
+      <c r="AN302">
+        <v>135100</v>
+      </c>
+      <c r="AS302" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT302" t="s">
+        <v>1080</v>
+      </c>
+      <c r="AU302" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV302" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="303" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>48</v>
+      </c>
+      <c r="B303" t="s">
+        <v>156</v>
+      </c>
+      <c r="C303" t="s">
+        <v>630</v>
+      </c>
+      <c r="D303" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E303" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F303" t="s">
+        <v>53</v>
+      </c>
+      <c r="G303" t="s">
+        <v>147</v>
+      </c>
+      <c r="H303" t="s">
+        <v>108</v>
+      </c>
+      <c r="I303">
+        <v>1490</v>
+      </c>
+      <c r="J303" t="s">
+        <v>56</v>
+      </c>
+      <c r="K303">
+        <v>62500</v>
+      </c>
+      <c r="L303">
+        <v>62500</v>
+      </c>
+      <c r="M303">
+        <v>36</v>
+      </c>
+      <c r="N303">
+        <v>31</v>
+      </c>
+      <c r="O303" t="s">
+        <v>907</v>
+      </c>
+      <c r="P303">
+        <v>62500</v>
+      </c>
+      <c r="Q303">
+        <v>62500</v>
+      </c>
+      <c r="R303" t="s">
+        <v>58</v>
+      </c>
+      <c r="S303">
+        <v>25</v>
+      </c>
+      <c r="T303">
+        <v>11</v>
+      </c>
+      <c r="U303">
+        <v>1</v>
+      </c>
+      <c r="V303">
+        <v>9</v>
+      </c>
+      <c r="W303" t="s">
+        <v>90</v>
+      </c>
+      <c r="X303" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y303" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z303" t="s">
+        <v>913</v>
+      </c>
+      <c r="AA303" t="s">
+        <v>913</v>
+      </c>
+      <c r="AB303" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC303" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD303" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE303" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF303" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG303">
+        <v>-56</v>
+      </c>
+      <c r="AH303">
+        <v>0</v>
+      </c>
+      <c r="AI303">
+        <v>0</v>
+      </c>
+      <c r="AJ303" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK303" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL303" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM303">
+        <v>973623</v>
+      </c>
+      <c r="AN303">
+        <v>134381</v>
+      </c>
+      <c r="AS303" t="s">
+        <v>140</v>
+      </c>
+      <c r="AT303" t="s">
+        <v>1084</v>
+      </c>
+      <c r="AV303" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="304" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>48</v>
+      </c>
+      <c r="B304" t="s">
+        <v>156</v>
+      </c>
+      <c r="C304" t="s">
+        <v>630</v>
+      </c>
+      <c r="D304" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E304" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F304" t="s">
+        <v>53</v>
+      </c>
+      <c r="G304" t="s">
+        <v>147</v>
+      </c>
+      <c r="H304" t="s">
+        <v>108</v>
+      </c>
+      <c r="I304">
+        <v>1490</v>
+      </c>
+      <c r="J304" t="s">
+        <v>56</v>
+      </c>
+      <c r="K304">
+        <v>62500</v>
+      </c>
+      <c r="L304">
+        <v>62500</v>
+      </c>
+      <c r="M304">
+        <v>36</v>
+      </c>
+      <c r="N304">
+        <v>31</v>
+      </c>
+      <c r="O304" t="s">
+        <v>907</v>
+      </c>
+      <c r="P304">
+        <v>62500</v>
+      </c>
+      <c r="Q304">
+        <v>62500</v>
+      </c>
+      <c r="R304" t="s">
+        <v>58</v>
+      </c>
+      <c r="S304">
+        <v>25</v>
+      </c>
+      <c r="T304">
+        <v>11</v>
+      </c>
+      <c r="U304">
+        <v>1</v>
+      </c>
+      <c r="V304">
+        <v>10</v>
+      </c>
+      <c r="W304" t="s">
+        <v>90</v>
+      </c>
+      <c r="X304" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y304" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z304" t="s">
+        <v>913</v>
+      </c>
+      <c r="AA304" t="s">
+        <v>913</v>
+      </c>
+      <c r="AB304" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC304" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD304" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE304" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF304" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG304">
+        <v>-56</v>
+      </c>
+      <c r="AH304">
+        <v>0</v>
+      </c>
+      <c r="AI304">
+        <v>0</v>
+      </c>
+      <c r="AJ304" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK304" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL304" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM304">
+        <v>973623</v>
+      </c>
+      <c r="AN304">
+        <v>134381</v>
+      </c>
+      <c r="AS304" t="s">
+        <v>140</v>
+      </c>
+      <c r="AT304" t="s">
+        <v>1084</v>
+      </c>
+      <c r="AV304" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="305" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>48</v>
+      </c>
+      <c r="B305" t="s">
+        <v>156</v>
+      </c>
+      <c r="C305" t="s">
+        <v>630</v>
+      </c>
+      <c r="D305" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E305" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F305" t="s">
+        <v>53</v>
+      </c>
+      <c r="G305" t="s">
+        <v>147</v>
+      </c>
+      <c r="H305" t="s">
+        <v>108</v>
+      </c>
+      <c r="I305">
+        <v>1490</v>
+      </c>
+      <c r="J305" t="s">
+        <v>56</v>
+      </c>
+      <c r="K305">
+        <v>62500</v>
+      </c>
+      <c r="L305">
+        <v>62500</v>
+      </c>
+      <c r="M305">
+        <v>36</v>
+      </c>
+      <c r="N305">
+        <v>31</v>
+      </c>
+      <c r="O305" t="s">
+        <v>907</v>
+      </c>
+      <c r="P305">
+        <v>62500</v>
+      </c>
+      <c r="Q305">
+        <v>62500</v>
+      </c>
+      <c r="R305" t="s">
+        <v>58</v>
+      </c>
+      <c r="S305">
+        <v>25</v>
+      </c>
+      <c r="T305">
+        <v>11</v>
+      </c>
+      <c r="U305">
+        <v>1</v>
+      </c>
+      <c r="V305">
+        <v>11</v>
+      </c>
+      <c r="W305" t="s">
+        <v>90</v>
+      </c>
+      <c r="X305" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y305" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z305" t="s">
+        <v>913</v>
+      </c>
+      <c r="AA305" t="s">
+        <v>913</v>
+      </c>
+      <c r="AB305" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC305" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD305" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE305" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF305" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG305">
+        <v>-56</v>
+      </c>
+      <c r="AH305">
+        <v>0</v>
+      </c>
+      <c r="AI305">
+        <v>0</v>
+      </c>
+      <c r="AJ305" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK305" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL305" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM305">
+        <v>973623</v>
+      </c>
+      <c r="AN305">
+        <v>134381</v>
+      </c>
+      <c r="AS305" t="s">
+        <v>140</v>
+      </c>
+      <c r="AT305" t="s">
+        <v>1084</v>
+      </c>
+      <c r="AV305" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="306" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>48</v>
+      </c>
+      <c r="B306" t="s">
+        <v>114</v>
+      </c>
+      <c r="C306" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D306" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E306" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F306" t="s">
+        <v>53</v>
+      </c>
+      <c r="G306" t="s">
+        <v>1089</v>
+      </c>
+      <c r="H306" t="s">
+        <v>108</v>
+      </c>
+      <c r="I306">
+        <v>2945</v>
+      </c>
+      <c r="J306" t="s">
+        <v>56</v>
+      </c>
+      <c r="K306">
+        <v>75833</v>
+      </c>
+      <c r="L306">
+        <v>75833</v>
+      </c>
+      <c r="M306">
+        <v>36</v>
+      </c>
+      <c r="N306">
+        <v>5</v>
+      </c>
+      <c r="O306" t="s">
+        <v>907</v>
+      </c>
+      <c r="P306">
+        <v>75833</v>
+      </c>
+      <c r="Q306">
+        <v>75833</v>
+      </c>
+      <c r="R306" t="s">
+        <v>58</v>
+      </c>
+      <c r="S306">
+        <v>31</v>
+      </c>
+      <c r="T306">
+        <v>5</v>
+      </c>
+      <c r="U306">
+        <v>1</v>
+      </c>
+      <c r="V306">
+        <v>5</v>
+      </c>
+      <c r="W306" t="s">
+        <v>90</v>
+      </c>
+      <c r="X306" t="s">
+        <v>378</v>
+      </c>
+      <c r="Y306" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z306" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA306" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB306" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD306" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE306" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF306" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG306">
+        <v>-30</v>
+      </c>
+      <c r="AH306">
+        <v>0</v>
+      </c>
+      <c r="AI306">
+        <v>0</v>
+      </c>
+      <c r="AJ306" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK306" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL306" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM306">
+        <v>973625</v>
+      </c>
+      <c r="AN306">
+        <v>134913</v>
+      </c>
+      <c r="AS306" t="s">
+        <v>152</v>
+      </c>
+      <c r="AT306" t="s">
+        <v>1090</v>
+      </c>
+      <c r="AU306" t="s">
+        <v>1091</v>
+      </c>
+      <c r="AV306" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="307" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>48</v>
+      </c>
+      <c r="B307" t="s">
+        <v>114</v>
+      </c>
+      <c r="C307" t="s">
+        <v>323</v>
+      </c>
+      <c r="D307" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E307" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F307" t="s">
+        <v>53</v>
+      </c>
+      <c r="G307" t="s">
+        <v>147</v>
+      </c>
+      <c r="H307" t="s">
+        <v>108</v>
+      </c>
+      <c r="I307">
+        <v>1839</v>
+      </c>
+      <c r="J307" t="s">
+        <v>56</v>
+      </c>
+      <c r="K307">
+        <v>110000</v>
+      </c>
+      <c r="L307">
+        <v>110000</v>
+      </c>
+      <c r="M307">
+        <v>60</v>
+      </c>
+      <c r="N307">
+        <v>5</v>
+      </c>
+      <c r="O307" t="s">
+        <v>907</v>
+      </c>
+      <c r="P307">
+        <v>110000</v>
+      </c>
+      <c r="Q307">
+        <v>110000</v>
+      </c>
+      <c r="R307" t="s">
+        <v>58</v>
+      </c>
+      <c r="S307">
+        <v>52</v>
+      </c>
+      <c r="T307">
+        <v>8</v>
+      </c>
+      <c r="U307">
+        <v>1</v>
+      </c>
+      <c r="V307">
+        <v>8</v>
+      </c>
+      <c r="W307" t="s">
+        <v>90</v>
+      </c>
+      <c r="X307" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y307" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z307" t="s">
+        <v>913</v>
+      </c>
+      <c r="AA307" t="s">
+        <v>913</v>
+      </c>
+      <c r="AB307" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD307" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE307" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF307" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG307">
+        <v>-30</v>
+      </c>
+      <c r="AH307">
+        <v>0</v>
+      </c>
+      <c r="AI307">
+        <v>0</v>
+      </c>
+      <c r="AJ307" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK307" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL307" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM307">
+        <v>973627</v>
+      </c>
+      <c r="AN307">
+        <v>134554</v>
+      </c>
+      <c r="AS307" t="s">
+        <v>222</v>
+      </c>
+      <c r="AT307" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AU307" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV307" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="308" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>48</v>
+      </c>
+      <c r="B308" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C308" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D308" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E308" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F308" t="s">
+        <v>386</v>
+      </c>
+      <c r="G308" t="s">
+        <v>386</v>
+      </c>
+      <c r="H308" t="s">
+        <v>108</v>
+      </c>
+      <c r="I308">
+        <v>3669</v>
+      </c>
+      <c r="J308" t="s">
+        <v>56</v>
+      </c>
+      <c r="K308">
+        <v>44444</v>
+      </c>
+      <c r="L308">
+        <v>44444</v>
+      </c>
+      <c r="M308">
+        <v>36</v>
+      </c>
+      <c r="N308">
+        <v>5</v>
+      </c>
+      <c r="O308" t="s">
+        <v>907</v>
+      </c>
+      <c r="P308">
+        <v>44444</v>
+      </c>
+      <c r="Q308">
+        <v>44444</v>
+      </c>
+      <c r="R308" t="s">
+        <v>58</v>
+      </c>
+      <c r="S308">
+        <v>33</v>
+      </c>
+      <c r="T308">
+        <v>3</v>
+      </c>
+      <c r="U308">
+        <v>1</v>
+      </c>
+      <c r="V308">
+        <v>3</v>
+      </c>
+      <c r="W308" t="s">
+        <v>90</v>
+      </c>
+      <c r="X308" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y308" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z308" t="s">
+        <v>1100</v>
+      </c>
+      <c r="AA308" t="s">
+        <v>1100</v>
+      </c>
+      <c r="AB308" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD308" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AE308" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF308" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG308">
+        <v>-30</v>
+      </c>
+      <c r="AH308">
+        <v>0</v>
+      </c>
+      <c r="AI308">
+        <v>0</v>
+      </c>
+      <c r="AJ308" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK308" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL308" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM308">
+        <v>973629</v>
+      </c>
+      <c r="AN308">
+        <v>135142</v>
+      </c>
+      <c r="AS308" t="s">
+        <v>177</v>
+      </c>
+      <c r="AT308" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AU308" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AV308" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="309" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>48</v>
+      </c>
+      <c r="B309" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C309" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D309" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E309" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F309" t="s">
+        <v>53</v>
+      </c>
+      <c r="G309" t="s">
+        <v>107</v>
+      </c>
+      <c r="H309" t="s">
+        <v>89</v>
+      </c>
+      <c r="I309">
+        <v>171</v>
+      </c>
+      <c r="J309" t="s">
+        <v>56</v>
+      </c>
+      <c r="K309">
+        <v>24000</v>
+      </c>
+      <c r="L309">
+        <v>24000</v>
+      </c>
+      <c r="M309">
+        <v>60</v>
+      </c>
+      <c r="N309">
+        <v>5</v>
+      </c>
+      <c r="O309" t="s">
+        <v>907</v>
+      </c>
+      <c r="P309">
+        <v>24000</v>
+      </c>
+      <c r="Q309">
+        <v>24000</v>
+      </c>
+      <c r="R309" t="s">
+        <v>58</v>
+      </c>
+      <c r="S309">
+        <v>41</v>
+      </c>
+      <c r="T309">
+        <v>19</v>
+      </c>
+      <c r="U309">
+        <v>1</v>
+      </c>
+      <c r="V309">
+        <v>19</v>
+      </c>
+      <c r="W309" t="s">
+        <v>90</v>
+      </c>
+      <c r="X309" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y309" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z309" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA309" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB309" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC309" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD309" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE309" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF309" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG309">
+        <v>-30</v>
+      </c>
+      <c r="AH309">
+        <v>0</v>
+      </c>
+      <c r="AI309">
+        <v>0</v>
+      </c>
+      <c r="AJ309" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK309" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL309" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM309">
+        <v>973631</v>
+      </c>
+      <c r="AN309">
+        <v>133299</v>
+      </c>
+      <c r="AS309" t="s">
+        <v>140</v>
+      </c>
+      <c r="AT309" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AU309" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AV309" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="310" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>48</v>
+      </c>
+      <c r="B310" t="s">
+        <v>243</v>
+      </c>
+      <c r="C310" t="s">
+        <v>187</v>
+      </c>
+      <c r="D310" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E310" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F310" t="s">
+        <v>53</v>
+      </c>
+      <c r="G310" t="s">
+        <v>198</v>
+      </c>
+      <c r="H310" t="s">
+        <v>108</v>
+      </c>
+      <c r="I310">
+        <v>3978</v>
+      </c>
+      <c r="J310" t="s">
+        <v>56</v>
+      </c>
+      <c r="K310">
+        <v>64111</v>
+      </c>
+      <c r="L310">
+        <v>64111</v>
+      </c>
+      <c r="M310">
+        <v>36</v>
+      </c>
+      <c r="N310">
+        <v>7</v>
+      </c>
+      <c r="O310" t="s">
+        <v>718</v>
+      </c>
+      <c r="P310">
+        <v>64000</v>
+      </c>
+      <c r="Q310">
+        <v>64000</v>
+      </c>
+      <c r="R310" t="s">
+        <v>58</v>
+      </c>
+      <c r="S310">
+        <v>35</v>
+      </c>
+      <c r="T310">
+        <v>2</v>
+      </c>
+      <c r="U310">
+        <v>1</v>
+      </c>
+      <c r="V310">
+        <v>2</v>
+      </c>
+      <c r="W310" t="s">
+        <v>90</v>
+      </c>
+      <c r="X310" t="s">
+        <v>378</v>
+      </c>
+      <c r="Y310" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z310" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA310" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB310" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD310" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE310" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF310" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG310">
+        <v>-2</v>
+      </c>
+      <c r="AH310">
+        <v>1</v>
+      </c>
+      <c r="AI310">
+        <v>0</v>
+      </c>
+      <c r="AJ310" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK310" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL310" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM310">
+        <v>973634</v>
+      </c>
+      <c r="AN310">
+        <v>135198</v>
+      </c>
+      <c r="AS310" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT310" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AU310" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV310" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="311" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>48</v>
+      </c>
+      <c r="B311" t="s">
+        <v>202</v>
+      </c>
+      <c r="C311" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D311" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E311" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F311" t="s">
+        <v>53</v>
+      </c>
+      <c r="G311" t="s">
+        <v>198</v>
+      </c>
+      <c r="H311" t="s">
+        <v>89</v>
+      </c>
+      <c r="I311">
+        <v>991</v>
+      </c>
+      <c r="J311" t="s">
+        <v>56</v>
+      </c>
+      <c r="K311">
+        <v>21333</v>
+      </c>
+      <c r="L311">
+        <v>21333</v>
+      </c>
+      <c r="M311">
+        <v>60</v>
+      </c>
+      <c r="N311">
+        <v>5</v>
+      </c>
+      <c r="O311" t="s">
+        <v>907</v>
+      </c>
+      <c r="P311">
+        <v>21000</v>
+      </c>
+      <c r="Q311">
+        <v>21000</v>
+      </c>
+      <c r="R311" t="s">
+        <v>58</v>
+      </c>
+      <c r="S311">
+        <v>46</v>
+      </c>
+      <c r="T311">
+        <v>15</v>
+      </c>
+      <c r="U311">
+        <v>1</v>
+      </c>
+      <c r="V311">
+        <v>15</v>
+      </c>
+      <c r="W311" t="s">
+        <v>7</v>
+      </c>
+      <c r="X311" t="s">
+        <v>378</v>
+      </c>
+      <c r="Y311" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z311" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA311" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB311" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC311" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD311" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE311" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF311" t="s">
+        <v>268</v>
+      </c>
+      <c r="AG311">
+        <v>0</v>
+      </c>
+      <c r="AH311">
+        <v>0</v>
+      </c>
+      <c r="AI311">
+        <v>0</v>
+      </c>
+      <c r="AJ311" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK311" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL311" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM311">
+        <v>973638</v>
+      </c>
+      <c r="AN311">
+        <v>133820</v>
+      </c>
+      <c r="AS311" t="s">
+        <v>140</v>
+      </c>
+      <c r="AT311" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AU311" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AV311" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="312" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>48</v>
+      </c>
+      <c r="B312" t="s">
+        <v>202</v>
+      </c>
+      <c r="C312" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D312" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E312" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F312" t="s">
+        <v>53</v>
+      </c>
+      <c r="G312" t="s">
+        <v>198</v>
+      </c>
+      <c r="H312" t="s">
+        <v>89</v>
+      </c>
+      <c r="I312">
+        <v>991</v>
+      </c>
+      <c r="J312" t="s">
+        <v>56</v>
+      </c>
+      <c r="K312">
+        <v>21333</v>
+      </c>
+      <c r="L312">
+        <v>21333</v>
+      </c>
+      <c r="M312">
+        <v>60</v>
+      </c>
+      <c r="N312">
+        <v>5</v>
+      </c>
+      <c r="O312" t="s">
+        <v>907</v>
+      </c>
+      <c r="P312">
+        <v>333</v>
+      </c>
+      <c r="Q312">
+        <v>333</v>
+      </c>
+      <c r="R312" t="s">
+        <v>58</v>
+      </c>
+      <c r="S312">
+        <v>46</v>
+      </c>
+      <c r="T312">
+        <v>15</v>
+      </c>
+      <c r="U312">
+        <v>1</v>
+      </c>
+      <c r="V312">
+        <v>14</v>
+      </c>
+      <c r="W312" t="s">
+        <v>7</v>
+      </c>
+      <c r="X312" t="s">
+        <v>378</v>
+      </c>
+      <c r="Y312" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z312" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA312" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB312" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC312" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD312" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE312" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF312" t="s">
+        <v>268</v>
+      </c>
+      <c r="AG312">
+        <v>0</v>
+      </c>
+      <c r="AH312">
+        <v>0</v>
+      </c>
+      <c r="AI312">
+        <v>0</v>
+      </c>
+      <c r="AJ312" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK312" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL312" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM312">
+        <v>973638</v>
+      </c>
+      <c r="AN312">
+        <v>133820</v>
+      </c>
+      <c r="AS312" t="s">
+        <v>140</v>
+      </c>
+      <c r="AT312" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AU312" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AV312" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="313" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>48</v>
+      </c>
+      <c r="B313" t="s">
+        <v>114</v>
+      </c>
+      <c r="C313" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D313" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E313" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F313" t="s">
+        <v>53</v>
+      </c>
+      <c r="G313" t="s">
+        <v>349</v>
+      </c>
+      <c r="H313" t="s">
+        <v>108</v>
+      </c>
+      <c r="I313">
+        <v>1821</v>
+      </c>
+      <c r="J313" t="s">
+        <v>56</v>
+      </c>
+      <c r="K313">
+        <v>54167</v>
+      </c>
+      <c r="L313">
+        <v>54167</v>
+      </c>
+      <c r="M313">
+        <v>36</v>
+      </c>
+      <c r="N313">
+        <v>5</v>
+      </c>
+      <c r="O313" t="s">
+        <v>907</v>
+      </c>
+      <c r="P313">
+        <v>264</v>
+      </c>
+      <c r="Q313">
+        <v>264</v>
+      </c>
+      <c r="R313" t="s">
+        <v>58</v>
+      </c>
+      <c r="S313">
+        <v>28</v>
+      </c>
+      <c r="T313">
+        <v>9</v>
+      </c>
+      <c r="U313">
+        <v>1</v>
+      </c>
+      <c r="V313">
+        <v>9</v>
+      </c>
+      <c r="W313" t="s">
+        <v>90</v>
+      </c>
+      <c r="X313" t="s">
+        <v>378</v>
+      </c>
+      <c r="Y313" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z313" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA313" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB313" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD313" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE313" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF313" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG313">
+        <v>-30</v>
+      </c>
+      <c r="AH313">
+        <v>0</v>
+      </c>
+      <c r="AI313">
+        <v>0</v>
+      </c>
+      <c r="AJ313" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK313" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL313" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM313">
+        <v>973640</v>
+      </c>
+      <c r="AN313">
+        <v>134542</v>
+      </c>
+      <c r="AS313" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT313" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AU313" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AV313" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="314" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>48</v>
+      </c>
+      <c r="B314" t="s">
+        <v>114</v>
+      </c>
+      <c r="C314" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D314" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E314" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F314" t="s">
+        <v>53</v>
+      </c>
+      <c r="G314" t="s">
+        <v>349</v>
+      </c>
+      <c r="H314" t="s">
+        <v>108</v>
+      </c>
+      <c r="I314">
+        <v>1821</v>
+      </c>
+      <c r="J314" t="s">
+        <v>56</v>
+      </c>
+      <c r="K314">
+        <v>54167</v>
+      </c>
+      <c r="L314">
+        <v>54167</v>
+      </c>
+      <c r="M314">
+        <v>36</v>
+      </c>
+      <c r="N314">
+        <v>5</v>
+      </c>
+      <c r="O314" t="s">
+        <v>907</v>
+      </c>
+      <c r="P314">
+        <v>53936</v>
+      </c>
+      <c r="Q314">
+        <v>53936</v>
+      </c>
+      <c r="R314" t="s">
+        <v>58</v>
+      </c>
+      <c r="S314">
+        <v>28</v>
+      </c>
+      <c r="T314">
+        <v>9</v>
+      </c>
+      <c r="U314">
+        <v>1</v>
+      </c>
+      <c r="V314">
+        <v>8</v>
+      </c>
+      <c r="W314" t="s">
+        <v>90</v>
+      </c>
+      <c r="X314" t="s">
+        <v>378</v>
+      </c>
+      <c r="Y314" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z314" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA314" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB314" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD314" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE314" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF314" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG314">
+        <v>-30</v>
+      </c>
+      <c r="AH314">
+        <v>0</v>
+      </c>
+      <c r="AI314">
+        <v>0</v>
+      </c>
+      <c r="AJ314" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK314" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL314" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM314">
+        <v>973640</v>
+      </c>
+      <c r="AN314">
+        <v>134542</v>
+      </c>
+      <c r="AS314" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT314" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AU314" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AV314" t="s">
+        <v>1123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AV249" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AV314" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010005AC72D710432E4590C56FAC8A5067F7" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df9b7e3cc90f1c832291ceb911da7a78">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f2597f6f-b030-4d48-9a06-75f8b747faaa" xmlns:ns3="327043bb-64a8-432c-b95b-048616f97fdb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="07d4e60082335aa0682d39ac9cb61a1f" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010005AC72D710432E4590C56FAC8A5067F7" ma:contentTypeVersion="11" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5789cff919fc8bc7d3ca9e3181d6c5e7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f2597f6f-b030-4d48-9a06-75f8b747faaa" xmlns:ns3="327043bb-64a8-432c-b95b-048616f97fdb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="37a5459c35dcd4e01f101c56aef12736" ns2:_="" ns3:_="">
     <xsd:import namespace="f2597f6f-b030-4d48-9a06-75f8b747faaa"/>
     <xsd:import namespace="327043bb-64a8-432c-b95b-048616f97fdb"/>
     <xsd:element name="properties">
@@ -35905,7 +45113,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6625b3b4-d90f-4b89-b6ae-ca1088d6f832" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6625b3b4-d90f-4b89-b6ae-ca1088d6f832" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -35954,8 +45162,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -36065,13 +45273,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F366EE7-D764-4AC8-99B9-4DE79132706F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45856F83-4C59-4467-AE0C-31F29AC6BD72}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E8DA573-B571-421A-965B-03DF4D621DEA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17108A9F-E8EE-4832-90F2-D0BEFD2EF6B1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{322DC7E9-9011-4D9D-803B-20702E79F73B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CE71E0A-36ED-4D62-BDA4-1F2F3CBE52B6}"/>
 </file>